--- a/AMD.xlsx
+++ b/AMD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{103F8454-0E76-4A31-8C58-D2D3D21887D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A64BFBA0-1300-41FA-A68B-6FE3BB12DF79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{88DDBE30-5603-410A-A895-5ECD92172F1B}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{88DDBE30-5603-410A-A895-5ECD92172F1B}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="53">
   <si>
     <t>numbers in mio USD</t>
   </si>
@@ -180,13 +180,22 @@
     <t xml:space="preserve">Partnership with OpenAi: </t>
   </si>
   <si>
-    <t>https://ir.amd.com/news-events/press-releases/detail/1260/amd-and-openai-announce-strategic-partnership-to-deploy-6-gigawatts-of-amd-gpus</t>
-  </si>
-  <si>
     <t>OpenAI to deploy 6 gigawatts of AMD based GPUs starting H2 26</t>
   </si>
   <si>
     <t>Warrant for OpenAi for 160 million shares</t>
+  </si>
+  <si>
+    <t>CEO:</t>
+  </si>
+  <si>
+    <t>Lisa Su</t>
+  </si>
+  <si>
+    <t>FY24</t>
+  </si>
+  <si>
+    <t>FY25</t>
   </si>
 </sst>
 </file>
@@ -288,7 +297,7 @@
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -309,6 +318,7 @@
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -648,111 +658,117 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A934EE6E-8823-4068-817D-B17F9B33324F}">
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.85546875" style="2" customWidth="1"/>
     <col min="2" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="2">
-        <v>226.55</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="G3" s="2" t="s">
+      <c r="K2" s="2">
+        <v>196.4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="J3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="3">
-        <v>1628.0415399999999</v>
-      </c>
-      <c r="I3" s="16" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B4" s="14" t="s">
+      <c r="K3" s="3">
+        <v>1630.4108430000001</v>
+      </c>
+      <c r="L3" s="17" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B4" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="3">
-        <f>+H2*H3</f>
-        <v>368832.810887</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="G5" s="2" t="s">
+      <c r="K4" s="3">
+        <f>+K2*K3</f>
+        <v>320212.68956520001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="J5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H5" s="3">
+      <c r="K5" s="3">
         <f>4808+2435</f>
         <v>7243</v>
       </c>
-      <c r="I5" s="16" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="G6" s="2" t="s">
+      <c r="L5" s="17" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="J6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H6" s="3">
+      <c r="K6" s="3">
         <f>2347+873</f>
         <v>3220</v>
       </c>
-      <c r="I6" s="16" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="G7" s="2" t="s">
+      <c r="L6" s="17" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="J7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H7" s="3">
-        <f>+H4-H5+H6</f>
-        <v>364809.810887</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K7" s="3">
+        <f>+K4-K5+K6</f>
+        <v>316189.68956520001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="J9" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B10" s="15" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B11" s="14" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B12" s="2" t="s">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B12" s="14" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B13" s="14" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B14" s="14" t="s">
-        <v>49</v>
-      </c>
-    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B4" r:id="rId1" xr:uid="{4921A678-BD64-4B53-9062-2B7D4F069433}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -809,6 +825,12 @@
       <c r="N2" s="10" t="s">
         <v>38</v>
       </c>
+      <c r="P2" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q2" s="17" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="3" spans="1:64" x14ac:dyDescent="0.2">
       <c r="B3" s="9" t="s">
@@ -845,8 +867,12 @@
       </c>
       <c r="N3" s="11"/>
       <c r="O3" s="11"/>
-      <c r="P3" s="11"/>
-      <c r="Q3" s="11"/>
+      <c r="P3" s="11">
+        <v>12579</v>
+      </c>
+      <c r="Q3" s="11">
+        <v>16635</v>
+      </c>
       <c r="R3" s="11"/>
       <c r="S3" s="11"/>
       <c r="T3" s="11"/>
@@ -930,8 +956,12 @@
       </c>
       <c r="N4" s="11"/>
       <c r="O4" s="11"/>
-      <c r="P4" s="11"/>
-      <c r="Q4" s="11"/>
+      <c r="P4" s="11">
+        <v>7054</v>
+      </c>
+      <c r="Q4" s="11">
+        <v>10640</v>
+      </c>
       <c r="R4" s="11"/>
       <c r="S4" s="11"/>
       <c r="T4" s="11"/>
@@ -1015,8 +1045,12 @@
       </c>
       <c r="N5" s="11"/>
       <c r="O5" s="11"/>
-      <c r="P5" s="11"/>
-      <c r="Q5" s="11"/>
+      <c r="P5" s="11">
+        <v>2595</v>
+      </c>
+      <c r="Q5" s="11">
+        <v>3910</v>
+      </c>
       <c r="R5" s="11"/>
       <c r="S5" s="11"/>
       <c r="T5" s="11"/>
@@ -1100,8 +1134,12 @@
       </c>
       <c r="N6" s="11"/>
       <c r="O6" s="11"/>
-      <c r="P6" s="11"/>
-      <c r="Q6" s="11"/>
+      <c r="P6" s="11">
+        <v>3557</v>
+      </c>
+      <c r="Q6" s="11">
+        <v>3454</v>
+      </c>
       <c r="R6" s="11"/>
       <c r="S6" s="11"/>
       <c r="T6" s="11"/>
@@ -1186,8 +1224,12 @@
       </c>
       <c r="N7" s="11"/>
       <c r="O7" s="11"/>
-      <c r="P7" s="11"/>
-      <c r="Q7" s="11"/>
+      <c r="P7" s="12">
+        <v>25785</v>
+      </c>
+      <c r="Q7" s="12">
+        <v>34639</v>
+      </c>
       <c r="R7" s="11"/>
       <c r="S7" s="11"/>
       <c r="T7" s="11"/>
@@ -1271,8 +1313,12 @@
       </c>
       <c r="N8" s="11"/>
       <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
+      <c r="P8" s="11">
+        <v>12114</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>16456</v>
+      </c>
       <c r="R8" s="11"/>
       <c r="S8" s="11"/>
       <c r="T8" s="11"/>
@@ -1356,8 +1402,12 @@
       </c>
       <c r="N9" s="11"/>
       <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
+      <c r="P9" s="11">
+        <v>946</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>1031</v>
+      </c>
       <c r="R9" s="11"/>
       <c r="S9" s="11"/>
       <c r="T9" s="11"/>
@@ -1439,7 +1489,7 @@
         <v>3419</v>
       </c>
       <c r="J10" s="11">
-        <f t="shared" ref="J10:N10" si="1">+J7-SUM(J8:J9)</f>
+        <f t="shared" ref="J10:Q10" si="1">+J7-SUM(J8:J9)</f>
         <v>0</v>
       </c>
       <c r="K10" s="11">
@@ -1459,8 +1509,14 @@
         <v>0</v>
       </c>
       <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
+      <c r="P10" s="11">
+        <f t="shared" si="1"/>
+        <v>12725</v>
+      </c>
+      <c r="Q10" s="11">
+        <f t="shared" si="1"/>
+        <v>17152</v>
+      </c>
       <c r="R10" s="11"/>
       <c r="S10" s="11"/>
       <c r="T10" s="11"/>
@@ -1544,8 +1600,12 @@
       </c>
       <c r="N11" s="11"/>
       <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
+      <c r="P11" s="11">
+        <v>6456</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>8091</v>
+      </c>
       <c r="R11" s="11"/>
       <c r="S11" s="11"/>
       <c r="T11" s="11"/>
@@ -1629,8 +1689,12 @@
       </c>
       <c r="N12" s="11"/>
       <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
+      <c r="P12" s="11">
+        <v>2735</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>4144</v>
+      </c>
       <c r="R12" s="11"/>
       <c r="S12" s="11"/>
       <c r="T12" s="11"/>
@@ -1714,8 +1778,12 @@
       </c>
       <c r="N13" s="11"/>
       <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
+      <c r="P13" s="11">
+        <v>1448</v>
+      </c>
+      <c r="Q13" s="11">
+        <v>1223</v>
+      </c>
       <c r="R13" s="11"/>
       <c r="S13" s="11"/>
       <c r="T13" s="11"/>
@@ -1799,8 +1867,12 @@
       </c>
       <c r="N14" s="11"/>
       <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="11"/>
+      <c r="P14" s="11">
+        <v>-186</v>
+      </c>
+      <c r="Q14" s="11">
+        <v>0</v>
+      </c>
       <c r="R14" s="11"/>
       <c r="S14" s="11"/>
       <c r="T14" s="11"/>
@@ -1882,7 +1954,7 @@
         <v>724</v>
       </c>
       <c r="J15" s="11">
-        <f t="shared" ref="J15:N15" si="3">+J10-SUM(J11:J13)+J14</f>
+        <f t="shared" ref="J15:Q15" si="3">+J10-SUM(J11:J13)+J14</f>
         <v>0</v>
       </c>
       <c r="K15" s="11">
@@ -1902,8 +1974,14 @@
         <v>0</v>
       </c>
       <c r="O15" s="11"/>
-      <c r="P15" s="11"/>
-      <c r="Q15" s="11"/>
+      <c r="P15" s="11">
+        <f t="shared" si="3"/>
+        <v>1900</v>
+      </c>
+      <c r="Q15" s="11">
+        <f t="shared" si="3"/>
+        <v>3694</v>
+      </c>
       <c r="R15" s="11"/>
       <c r="S15" s="11"/>
       <c r="T15" s="11"/>
@@ -1987,8 +2065,12 @@
       </c>
       <c r="N16" s="11"/>
       <c r="O16" s="11"/>
-      <c r="P16" s="11"/>
-      <c r="Q16" s="11"/>
+      <c r="P16" s="11">
+        <v>92</v>
+      </c>
+      <c r="Q16" s="11">
+        <v>131</v>
+      </c>
       <c r="R16" s="11"/>
       <c r="S16" s="11"/>
       <c r="T16" s="11"/>
@@ -2072,8 +2154,12 @@
       </c>
       <c r="N17" s="11"/>
       <c r="O17" s="11"/>
-      <c r="P17" s="11"/>
-      <c r="Q17" s="11"/>
+      <c r="P17" s="11">
+        <v>181</v>
+      </c>
+      <c r="Q17" s="11">
+        <v>577</v>
+      </c>
       <c r="R17" s="11"/>
       <c r="S17" s="11"/>
       <c r="T17" s="11"/>
@@ -2155,7 +2241,7 @@
         <v>737</v>
       </c>
       <c r="J18" s="11">
-        <f t="shared" ref="J18:N18" si="5">+J15-J16+J17</f>
+        <f t="shared" ref="J18:Q18" si="5">+J15-J16+J17</f>
         <v>0</v>
       </c>
       <c r="K18" s="11">
@@ -2175,8 +2261,14 @@
         <v>0</v>
       </c>
       <c r="O18" s="11"/>
-      <c r="P18" s="11"/>
-      <c r="Q18" s="11"/>
+      <c r="P18" s="11">
+        <f t="shared" si="5"/>
+        <v>1989</v>
+      </c>
+      <c r="Q18" s="11">
+        <f t="shared" si="5"/>
+        <v>4140</v>
+      </c>
       <c r="R18" s="11"/>
       <c r="S18" s="11"/>
       <c r="T18" s="11"/>
@@ -2260,8 +2352,12 @@
       </c>
       <c r="N19" s="11"/>
       <c r="O19" s="11"/>
-      <c r="P19" s="11"/>
-      <c r="Q19" s="11"/>
+      <c r="P19" s="11">
+        <v>381</v>
+      </c>
+      <c r="Q19" s="11">
+        <v>-103</v>
+      </c>
       <c r="R19" s="11"/>
       <c r="S19" s="11"/>
       <c r="T19" s="11"/>
@@ -2347,8 +2443,13 @@
       </c>
       <c r="N20" s="11"/>
       <c r="O20" s="11"/>
-      <c r="P20" s="11"/>
-      <c r="Q20" s="11"/>
+      <c r="P20" s="11">
+        <v>33</v>
+      </c>
+      <c r="Q20" s="11">
+        <f>26+66</f>
+        <v>92</v>
+      </c>
       <c r="R20" s="11"/>
       <c r="S20" s="11"/>
       <c r="T20" s="11"/>
@@ -2430,7 +2531,7 @@
         <v>771</v>
       </c>
       <c r="J21" s="11">
-        <f t="shared" ref="J21:N21" si="7">+J18-J19+J20</f>
+        <f t="shared" ref="J21:Q21" si="7">+J18-J19+J20</f>
         <v>0</v>
       </c>
       <c r="K21" s="11">
@@ -2450,8 +2551,14 @@
         <v>0</v>
       </c>
       <c r="O21" s="11"/>
-      <c r="P21" s="11"/>
-      <c r="Q21" s="11"/>
+      <c r="P21" s="11">
+        <f t="shared" si="7"/>
+        <v>1641</v>
+      </c>
+      <c r="Q21" s="11">
+        <f t="shared" si="7"/>
+        <v>4335</v>
+      </c>
       <c r="R21" s="11"/>
       <c r="S21" s="11"/>
       <c r="T21" s="11"/>
@@ -2597,7 +2704,7 @@
         <v>0.47592592592592592</v>
       </c>
       <c r="J23" s="7" t="e">
-        <f t="shared" ref="J23:N23" si="9">+J21/J24</f>
+        <f t="shared" ref="J23:Q23" si="9">+J21/J24</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K23" s="7">
@@ -2617,8 +2724,14 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O23" s="3"/>
-      <c r="P23" s="3"/>
-      <c r="Q23" s="3"/>
+      <c r="P23" s="7">
+        <f t="shared" si="9"/>
+        <v>1.0129629629629631</v>
+      </c>
+      <c r="Q23" s="7">
+        <f t="shared" si="9"/>
+        <v>2.6693349753694582</v>
+      </c>
       <c r="R23" s="3"/>
       <c r="S23" s="3"/>
       <c r="T23" s="3"/>
@@ -2702,8 +2815,12 @@
       </c>
       <c r="N24" s="3"/>
       <c r="O24" s="3"/>
-      <c r="P24" s="3"/>
-      <c r="Q24" s="3"/>
+      <c r="P24" s="3">
+        <v>1620</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>1624</v>
+      </c>
       <c r="R24" s="3"/>
       <c r="S24" s="3"/>
       <c r="T24" s="3"/>
@@ -2858,7 +2975,10 @@
       </c>
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
-      <c r="Q26" s="3"/>
+      <c r="Q26" s="13">
+        <f>+Q7/P7-1</f>
+        <v>0.3433779329067288</v>
+      </c>
       <c r="R26" s="3"/>
       <c r="S26" s="3"/>
       <c r="T26" s="3"/>
@@ -2960,8 +3080,14 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O27" s="3"/>
-      <c r="P27" s="3"/>
-      <c r="Q27" s="3"/>
+      <c r="P27" s="8">
+        <f t="shared" ref="P27:Q27" si="14">+P10/P7</f>
+        <v>0.49350397517936784</v>
+      </c>
+      <c r="Q27" s="8">
+        <f t="shared" si="14"/>
+        <v>0.49516441005802708</v>
+      </c>
       <c r="R27" s="3"/>
       <c r="S27" s="3"/>
       <c r="T27" s="3"/>
@@ -3015,27 +3141,27 @@
         <v>33</v>
       </c>
       <c r="C28" s="8">
-        <f t="shared" ref="C28:H28" si="14">+C15/C7</f>
+        <f t="shared" ref="C28:H28" si="15">+C15/C7</f>
         <v>-2.7087614421819541E-2</v>
       </c>
       <c r="D28" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-3.7320395596193321E-3</v>
       </c>
       <c r="E28" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>3.8620689655172416E-2</v>
       </c>
       <c r="F28" s="8" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G28" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>6.5777452950849628E-3</v>
       </c>
       <c r="H28" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>4.6101113967437872E-2</v>
       </c>
       <c r="I28" s="8">
@@ -3043,28 +3169,34 @@
         <v>0.10617392579557119</v>
       </c>
       <c r="J28" s="8" t="e">
-        <f t="shared" ref="J28:N28" si="15">+J15/J7</f>
+        <f t="shared" ref="J28:N28" si="16">+J15/J7</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K28" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.10836246302769562</v>
       </c>
       <c r="L28" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-1.7436564736499675E-2</v>
       </c>
       <c r="M28" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.13735669478693488</v>
       </c>
       <c r="N28" s="8" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O28" s="3"/>
-      <c r="P28" s="3"/>
-      <c r="Q28" s="3"/>
+      <c r="P28" s="8">
+        <f t="shared" ref="P28:Q28" si="17">+P15/P7</f>
+        <v>7.3686251696722896E-2</v>
+      </c>
+      <c r="Q28" s="8">
+        <f t="shared" si="17"/>
+        <v>0.10664280146655504</v>
+      </c>
       <c r="R28" s="3"/>
       <c r="S28" s="3"/>
       <c r="T28" s="3"/>
@@ -3118,27 +3250,27 @@
         <v>34</v>
       </c>
       <c r="C29" s="8">
-        <f t="shared" ref="C29:H29" si="16">+C19/C18</f>
+        <f t="shared" ref="C29:H29" si="18">+C19/C18</f>
         <v>-0.10236220472440945</v>
       </c>
       <c r="D29" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>11.5</v>
       </c>
       <c r="E29" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-0.1517509727626459</v>
       </c>
       <c r="F29" s="8" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G29" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-0.8125</v>
       </c>
       <c r="H29" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.13712374581939799</v>
       </c>
       <c r="I29" s="8">
@@ -3146,28 +3278,34 @@
         <v>-3.6635006784260515E-2</v>
       </c>
       <c r="J29" s="8" t="e">
-        <f t="shared" ref="J29:N29" si="17">+J19/J18</f>
+        <f t="shared" ref="J29:N29" si="19">+J19/J18</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K29" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0.14909090909090908</v>
       </c>
       <c r="L29" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>11.27027027027027</v>
       </c>
       <c r="M29" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0.11634980988593156</v>
       </c>
       <c r="N29" s="8" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O29" s="3"/>
-      <c r="P29" s="3"/>
-      <c r="Q29" s="3"/>
+      <c r="P29" s="8">
+        <f t="shared" ref="P29:Q29" si="20">+P19/P18</f>
+        <v>0.19155354449472098</v>
+      </c>
+      <c r="Q29" s="8">
+        <f t="shared" si="20"/>
+        <v>-2.4879227053140097E-2</v>
+      </c>
       <c r="R29" s="3"/>
       <c r="S29" s="3"/>
       <c r="T29" s="3"/>

--- a/AMD.xlsx
+++ b/AMD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A64BFBA0-1300-41FA-A68B-6FE3BB12DF79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DC0D06D-4B68-411C-9021-BFB1E001EDAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{88DDBE30-5603-410A-A895-5ECD92172F1B}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{88DDBE30-5603-410A-A895-5ECD92172F1B}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="57">
   <si>
     <t>numbers in mio USD</t>
   </si>
@@ -197,6 +197,18 @@
   <si>
     <t>FY25</t>
   </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
+  </si>
 </sst>
 </file>
 
@@ -205,13 +217,19 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\)"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -294,31 +312,34 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -678,7 +699,7 @@
         <v>1</v>
       </c>
       <c r="K2" s="2">
-        <v>196.4</v>
+        <v>514.87</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
@@ -686,10 +707,10 @@
         <v>2</v>
       </c>
       <c r="K3" s="3">
-        <v>1630.4108430000001</v>
-      </c>
-      <c r="L3" s="17" t="s">
-        <v>38</v>
+        <v>1630.600639</v>
+      </c>
+      <c r="L3" s="18" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
@@ -701,7 +722,7 @@
       </c>
       <c r="K4" s="3">
         <f>+K2*K3</f>
-        <v>320212.68956520001</v>
+        <v>839547.35100192996</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
@@ -709,11 +730,11 @@
         <v>4</v>
       </c>
       <c r="K5" s="3">
-        <f>4808+2435</f>
-        <v>7243</v>
-      </c>
-      <c r="L5" s="17" t="s">
-        <v>38</v>
+        <f>5575+6762</f>
+        <v>12337</v>
+      </c>
+      <c r="L5" s="18" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
@@ -721,11 +742,11 @@
         <v>5</v>
       </c>
       <c r="K6" s="3">
-        <f>2347+873</f>
-        <v>3220</v>
-      </c>
-      <c r="L6" s="17" t="s">
-        <v>38</v>
+        <f>874+2350</f>
+        <v>3224</v>
+      </c>
+      <c r="L6" s="18" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
@@ -734,7 +755,7 @@
       </c>
       <c r="K7" s="3">
         <f>+K4-K5+K6</f>
-        <v>316189.68956520001</v>
+        <v>830434.35100192996</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
@@ -775,7 +796,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3C22265-4306-401D-803C-CB5EEC240F05}">
-  <dimension ref="A1:BL170"/>
+  <dimension ref="A1:BP170"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="2" customWidth="1"/>
@@ -783,12 +804,12 @@
     <col min="3" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:64" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:64" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:68" x14ac:dyDescent="0.2">
       <c r="C2" s="4" t="s">
         <v>10</v>
       </c>
@@ -825,14 +846,26 @@
       <c r="N2" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="P2" s="17" t="s">
+      <c r="O2" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="P2" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q2" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="R2" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="T2" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="Q2" s="17" t="s">
+      <c r="U2" s="17" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:64" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:68" x14ac:dyDescent="0.2">
       <c r="B3" s="9" t="s">
         <v>40</v>
       </c>
@@ -855,7 +888,10 @@
       <c r="I3" s="11">
         <v>3549</v>
       </c>
-      <c r="J3" s="11"/>
+      <c r="J3" s="11">
+        <f>+T3-SUM(G3:I3)</f>
+        <v>3859</v>
+      </c>
       <c r="K3" s="11">
         <v>3674</v>
       </c>
@@ -865,25 +901,30 @@
       <c r="M3" s="11">
         <v>4341</v>
       </c>
-      <c r="N3" s="11"/>
-      <c r="O3" s="11"/>
-      <c r="P3" s="11">
-        <v>12579</v>
-      </c>
-      <c r="Q3" s="11">
-        <v>16635</v>
-      </c>
+      <c r="N3" s="11">
+        <f>+U3-SUM(K3:M3)</f>
+        <v>5380</v>
+      </c>
+      <c r="O3" s="11">
+        <v>5775</v>
+      </c>
+      <c r="P3" s="11"/>
+      <c r="Q3" s="11"/>
       <c r="R3" s="11"/>
       <c r="S3" s="11"/>
-      <c r="T3" s="11"/>
-      <c r="U3" s="11"/>
+      <c r="T3" s="11">
+        <v>12579</v>
+      </c>
+      <c r="U3" s="11">
+        <v>16635</v>
+      </c>
       <c r="V3" s="11"/>
       <c r="W3" s="11"/>
       <c r="X3" s="11"/>
-      <c r="Y3" s="3"/>
-      <c r="Z3" s="3"/>
-      <c r="AA3" s="3"/>
-      <c r="AB3" s="3"/>
+      <c r="Y3" s="11"/>
+      <c r="Z3" s="11"/>
+      <c r="AA3" s="11"/>
+      <c r="AB3" s="11"/>
       <c r="AC3" s="3"/>
       <c r="AD3" s="3"/>
       <c r="AE3" s="3"/>
@@ -920,8 +961,12 @@
       <c r="BJ3" s="3"/>
       <c r="BK3" s="3"/>
       <c r="BL3" s="3"/>
-    </row>
-    <row r="4" spans="1:64" x14ac:dyDescent="0.2">
+      <c r="BM3" s="3"/>
+      <c r="BN3" s="3"/>
+      <c r="BO3" s="3"/>
+      <c r="BP3" s="3"/>
+    </row>
+    <row r="4" spans="1:68" x14ac:dyDescent="0.2">
       <c r="B4" s="9" t="s">
         <v>41</v>
       </c>
@@ -944,7 +989,10 @@
       <c r="I4" s="11">
         <v>1881</v>
       </c>
-      <c r="J4" s="11"/>
+      <c r="J4" s="11">
+        <f t="shared" ref="J4:J20" si="0">+T4-SUM(G4:I4)</f>
+        <v>2313</v>
+      </c>
       <c r="K4" s="11">
         <v>2294</v>
       </c>
@@ -954,25 +1002,30 @@
       <c r="M4" s="11">
         <v>2750</v>
       </c>
-      <c r="N4" s="11"/>
-      <c r="O4" s="11"/>
-      <c r="P4" s="11">
-        <v>7054</v>
-      </c>
-      <c r="Q4" s="11">
-        <v>10640</v>
-      </c>
+      <c r="N4" s="11">
+        <f t="shared" ref="N4:N20" si="1">+U4-SUM(K4:M4)</f>
+        <v>3097</v>
+      </c>
+      <c r="O4" s="11">
+        <v>2885</v>
+      </c>
+      <c r="P4" s="11"/>
+      <c r="Q4" s="11"/>
       <c r="R4" s="11"/>
       <c r="S4" s="11"/>
-      <c r="T4" s="11"/>
-      <c r="U4" s="11"/>
+      <c r="T4" s="11">
+        <v>7054</v>
+      </c>
+      <c r="U4" s="11">
+        <v>10640</v>
+      </c>
       <c r="V4" s="11"/>
       <c r="W4" s="11"/>
       <c r="X4" s="11"/>
-      <c r="Y4" s="3"/>
-      <c r="Z4" s="3"/>
-      <c r="AA4" s="3"/>
-      <c r="AB4" s="3"/>
+      <c r="Y4" s="11"/>
+      <c r="Z4" s="11"/>
+      <c r="AA4" s="11"/>
+      <c r="AB4" s="11"/>
       <c r="AC4" s="3"/>
       <c r="AD4" s="3"/>
       <c r="AE4" s="3"/>
@@ -1009,8 +1062,12 @@
       <c r="BJ4" s="3"/>
       <c r="BK4" s="3"/>
       <c r="BL4" s="3"/>
-    </row>
-    <row r="5" spans="1:64" x14ac:dyDescent="0.2">
+      <c r="BM4" s="3"/>
+      <c r="BN4" s="3"/>
+      <c r="BO4" s="3"/>
+      <c r="BP4" s="3"/>
+    </row>
+    <row r="5" spans="1:68" x14ac:dyDescent="0.2">
       <c r="B5" s="9" t="s">
         <v>42</v>
       </c>
@@ -1033,7 +1090,10 @@
       <c r="I5" s="11">
         <v>462</v>
       </c>
-      <c r="J5" s="11"/>
+      <c r="J5" s="11">
+        <f t="shared" si="0"/>
+        <v>563</v>
+      </c>
       <c r="K5" s="11">
         <v>647</v>
       </c>
@@ -1043,25 +1103,30 @@
       <c r="M5" s="11">
         <v>1298</v>
       </c>
-      <c r="N5" s="11"/>
-      <c r="O5" s="11"/>
-      <c r="P5" s="11">
-        <v>2595</v>
-      </c>
-      <c r="Q5" s="11">
-        <v>3910</v>
-      </c>
+      <c r="N5" s="11">
+        <f t="shared" si="1"/>
+        <v>843</v>
+      </c>
+      <c r="O5" s="11">
+        <v>720</v>
+      </c>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="11"/>
       <c r="R5" s="11"/>
       <c r="S5" s="11"/>
-      <c r="T5" s="11"/>
-      <c r="U5" s="11"/>
+      <c r="T5" s="11">
+        <v>2595</v>
+      </c>
+      <c r="U5" s="11">
+        <v>3910</v>
+      </c>
       <c r="V5" s="11"/>
       <c r="W5" s="11"/>
       <c r="X5" s="11"/>
-      <c r="Y5" s="3"/>
-      <c r="Z5" s="3"/>
-      <c r="AA5" s="3"/>
-      <c r="AB5" s="3"/>
+      <c r="Y5" s="11"/>
+      <c r="Z5" s="11"/>
+      <c r="AA5" s="11"/>
+      <c r="AB5" s="11"/>
       <c r="AC5" s="3"/>
       <c r="AD5" s="3"/>
       <c r="AE5" s="3"/>
@@ -1098,8 +1163,12 @@
       <c r="BJ5" s="3"/>
       <c r="BK5" s="3"/>
       <c r="BL5" s="3"/>
-    </row>
-    <row r="6" spans="1:64" x14ac:dyDescent="0.2">
+      <c r="BM5" s="3"/>
+      <c r="BN5" s="3"/>
+      <c r="BO5" s="3"/>
+      <c r="BP5" s="3"/>
+    </row>
+    <row r="6" spans="1:68" x14ac:dyDescent="0.2">
       <c r="B6" s="9" t="s">
         <v>43</v>
       </c>
@@ -1122,7 +1191,10 @@
       <c r="I6" s="11">
         <v>927</v>
       </c>
-      <c r="J6" s="11"/>
+      <c r="J6" s="11">
+        <f t="shared" si="0"/>
+        <v>923</v>
+      </c>
       <c r="K6" s="11">
         <v>823</v>
       </c>
@@ -1132,25 +1204,30 @@
       <c r="M6" s="11">
         <v>857</v>
       </c>
-      <c r="N6" s="11"/>
-      <c r="O6" s="11"/>
-      <c r="P6" s="11">
-        <v>3557</v>
-      </c>
-      <c r="Q6" s="11">
-        <v>3454</v>
-      </c>
+      <c r="N6" s="11">
+        <f t="shared" si="1"/>
+        <v>950</v>
+      </c>
+      <c r="O6" s="11">
+        <v>873</v>
+      </c>
+      <c r="P6" s="11"/>
+      <c r="Q6" s="11"/>
       <c r="R6" s="11"/>
       <c r="S6" s="11"/>
-      <c r="T6" s="11"/>
-      <c r="U6" s="11"/>
+      <c r="T6" s="11">
+        <v>3557</v>
+      </c>
+      <c r="U6" s="11">
+        <v>3454</v>
+      </c>
       <c r="V6" s="11"/>
       <c r="W6" s="11"/>
       <c r="X6" s="11"/>
-      <c r="Y6" s="3"/>
-      <c r="Z6" s="3"/>
-      <c r="AA6" s="3"/>
-      <c r="AB6" s="3"/>
+      <c r="Y6" s="11"/>
+      <c r="Z6" s="11"/>
+      <c r="AA6" s="11"/>
+      <c r="AB6" s="11"/>
       <c r="AC6" s="3"/>
       <c r="AD6" s="3"/>
       <c r="AE6" s="3"/>
@@ -1187,8 +1264,12 @@
       <c r="BJ6" s="3"/>
       <c r="BK6" s="3"/>
       <c r="BL6" s="3"/>
-    </row>
-    <row r="7" spans="1:64" x14ac:dyDescent="0.2">
+      <c r="BM6" s="3"/>
+      <c r="BN6" s="3"/>
+      <c r="BO6" s="3"/>
+      <c r="BP6" s="3"/>
+    </row>
+    <row r="7" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
       <c r="B7" s="1" t="s">
         <v>17</v>
@@ -1212,7 +1293,10 @@
       <c r="I7" s="12">
         <v>6819</v>
       </c>
-      <c r="J7" s="12"/>
+      <c r="J7" s="12">
+        <f t="shared" si="0"/>
+        <v>7658</v>
+      </c>
       <c r="K7" s="12">
         <v>7438</v>
       </c>
@@ -1222,25 +1306,30 @@
       <c r="M7" s="12">
         <v>9246</v>
       </c>
-      <c r="N7" s="11"/>
-      <c r="O7" s="11"/>
-      <c r="P7" s="12">
-        <v>25785</v>
-      </c>
-      <c r="Q7" s="12">
-        <v>34639</v>
-      </c>
+      <c r="N7" s="12">
+        <f t="shared" si="1"/>
+        <v>10270</v>
+      </c>
+      <c r="O7" s="12">
+        <v>10253</v>
+      </c>
+      <c r="P7" s="11"/>
+      <c r="Q7" s="11"/>
       <c r="R7" s="11"/>
       <c r="S7" s="11"/>
-      <c r="T7" s="11"/>
-      <c r="U7" s="11"/>
+      <c r="T7" s="12">
+        <v>25785</v>
+      </c>
+      <c r="U7" s="12">
+        <v>34639</v>
+      </c>
       <c r="V7" s="11"/>
       <c r="W7" s="11"/>
       <c r="X7" s="11"/>
-      <c r="Y7" s="3"/>
-      <c r="Z7" s="3"/>
-      <c r="AA7" s="3"/>
-      <c r="AB7" s="3"/>
+      <c r="Y7" s="11"/>
+      <c r="Z7" s="11"/>
+      <c r="AA7" s="11"/>
+      <c r="AB7" s="11"/>
       <c r="AC7" s="3"/>
       <c r="AD7" s="3"/>
       <c r="AE7" s="3"/>
@@ -1277,8 +1366,12 @@
       <c r="BJ7" s="3"/>
       <c r="BK7" s="3"/>
       <c r="BL7" s="3"/>
-    </row>
-    <row r="8" spans="1:64" x14ac:dyDescent="0.2">
+      <c r="BM7" s="3"/>
+      <c r="BN7" s="3"/>
+      <c r="BO7" s="3"/>
+      <c r="BP7" s="3"/>
+    </row>
+    <row r="8" spans="1:68" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
         <v>18</v>
       </c>
@@ -1301,7 +1394,10 @@
       <c r="I8" s="11">
         <v>3167</v>
       </c>
-      <c r="J8" s="11"/>
+      <c r="J8" s="11">
+        <f t="shared" si="0"/>
+        <v>3524</v>
+      </c>
       <c r="K8" s="11">
         <v>3451</v>
       </c>
@@ -1311,25 +1407,30 @@
       <c r="M8" s="11">
         <v>4206</v>
       </c>
-      <c r="N8" s="11"/>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11">
-        <v>12114</v>
-      </c>
-      <c r="Q8" s="11">
-        <v>16456</v>
-      </c>
+      <c r="N8" s="11">
+        <f t="shared" si="1"/>
+        <v>4433</v>
+      </c>
+      <c r="O8" s="11">
+        <v>4576</v>
+      </c>
+      <c r="P8" s="11"/>
+      <c r="Q8" s="11"/>
       <c r="R8" s="11"/>
       <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="T8" s="11">
+        <v>12114</v>
+      </c>
+      <c r="U8" s="11">
+        <v>16456</v>
+      </c>
       <c r="V8" s="11"/>
       <c r="W8" s="11"/>
       <c r="X8" s="11"/>
-      <c r="Y8" s="3"/>
-      <c r="Z8" s="3"/>
-      <c r="AA8" s="3"/>
-      <c r="AB8" s="3"/>
+      <c r="Y8" s="11"/>
+      <c r="Z8" s="11"/>
+      <c r="AA8" s="11"/>
+      <c r="AB8" s="11"/>
       <c r="AC8" s="3"/>
       <c r="AD8" s="3"/>
       <c r="AE8" s="3"/>
@@ -1366,8 +1467,12 @@
       <c r="BJ8" s="3"/>
       <c r="BK8" s="3"/>
       <c r="BL8" s="3"/>
-    </row>
-    <row r="9" spans="1:64" x14ac:dyDescent="0.2">
+      <c r="BM8" s="3"/>
+      <c r="BN8" s="3"/>
+      <c r="BO8" s="3"/>
+      <c r="BP8" s="3"/>
+    </row>
+    <row r="9" spans="1:68" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
         <v>19</v>
       </c>
@@ -1390,7 +1495,10 @@
       <c r="I9" s="11">
         <v>233</v>
       </c>
-      <c r="J9" s="11"/>
+      <c r="J9" s="11">
+        <f t="shared" si="0"/>
+        <v>252</v>
+      </c>
       <c r="K9" s="11">
         <v>251</v>
       </c>
@@ -1400,25 +1508,30 @@
       <c r="M9" s="11">
         <v>260</v>
       </c>
-      <c r="N9" s="11"/>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11">
-        <v>946</v>
-      </c>
-      <c r="Q9" s="11">
-        <v>1031</v>
-      </c>
+      <c r="N9" s="11">
+        <f t="shared" si="1"/>
+        <v>260</v>
+      </c>
+      <c r="O9" s="11">
+        <v>261</v>
+      </c>
+      <c r="P9" s="11"/>
+      <c r="Q9" s="11"/>
       <c r="R9" s="11"/>
       <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="T9" s="11">
+        <v>946</v>
+      </c>
+      <c r="U9" s="11">
+        <v>1031</v>
+      </c>
       <c r="V9" s="11"/>
       <c r="W9" s="11"/>
       <c r="X9" s="11"/>
-      <c r="Y9" s="3"/>
-      <c r="Z9" s="3"/>
-      <c r="AA9" s="3"/>
-      <c r="AB9" s="3"/>
+      <c r="Y9" s="11"/>
+      <c r="Z9" s="11"/>
+      <c r="AA9" s="11"/>
+      <c r="AB9" s="11"/>
       <c r="AC9" s="3"/>
       <c r="AD9" s="3"/>
       <c r="AE9" s="3"/>
@@ -1455,33 +1568,37 @@
       <c r="BJ9" s="3"/>
       <c r="BK9" s="3"/>
       <c r="BL9" s="3"/>
-    </row>
-    <row r="10" spans="1:64" x14ac:dyDescent="0.2">
+      <c r="BM9" s="3"/>
+      <c r="BN9" s="3"/>
+      <c r="BO9" s="3"/>
+      <c r="BP9" s="3"/>
+    </row>
+    <row r="10" spans="1:68" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C10" s="11">
-        <f t="shared" ref="C10:H10" si="0">+C7-SUM(C8:C9)</f>
+        <f t="shared" ref="C10:H10" si="2">+C7-SUM(C8:C9)</f>
         <v>2359</v>
       </c>
       <c r="D10" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2443</v>
       </c>
       <c r="E10" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2747</v>
       </c>
       <c r="F10" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G10" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2560</v>
       </c>
       <c r="H10" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2864</v>
       </c>
       <c r="I10" s="11">
@@ -1489,45 +1606,48 @@
         <v>3419</v>
       </c>
       <c r="J10" s="11">
-        <f t="shared" ref="J10:Q10" si="1">+J7-SUM(J8:J9)</f>
-        <v>0</v>
+        <f t="shared" ref="J10:U10" si="3">+J7-SUM(J8:J9)</f>
+        <v>3882</v>
       </c>
       <c r="K10" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>3736</v>
       </c>
       <c r="L10" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>3059</v>
       </c>
       <c r="M10" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>4780</v>
       </c>
       <c r="N10" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11">
-        <f t="shared" si="1"/>
-        <v>12725</v>
-      </c>
-      <c r="Q10" s="11">
-        <f t="shared" si="1"/>
-        <v>17152</v>
-      </c>
+        <f t="shared" si="3"/>
+        <v>5577</v>
+      </c>
+      <c r="O10" s="11">
+        <f t="shared" si="3"/>
+        <v>5416</v>
+      </c>
+      <c r="P10" s="11"/>
+      <c r="Q10" s="11"/>
       <c r="R10" s="11"/>
       <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
+      <c r="T10" s="11">
+        <f t="shared" si="3"/>
+        <v>12725</v>
+      </c>
+      <c r="U10" s="11">
+        <f t="shared" si="3"/>
+        <v>17152</v>
+      </c>
       <c r="V10" s="11"/>
       <c r="W10" s="11"/>
       <c r="X10" s="11"/>
-      <c r="Y10" s="3"/>
-      <c r="Z10" s="3"/>
-      <c r="AA10" s="3"/>
-      <c r="AB10" s="3"/>
+      <c r="Y10" s="11"/>
+      <c r="Z10" s="11"/>
+      <c r="AA10" s="11"/>
+      <c r="AB10" s="11"/>
       <c r="AC10" s="3"/>
       <c r="AD10" s="3"/>
       <c r="AE10" s="3"/>
@@ -1564,8 +1684,12 @@
       <c r="BJ10" s="3"/>
       <c r="BK10" s="3"/>
       <c r="BL10" s="3"/>
-    </row>
-    <row r="11" spans="1:64" x14ac:dyDescent="0.2">
+      <c r="BM10" s="3"/>
+      <c r="BN10" s="3"/>
+      <c r="BO10" s="3"/>
+      <c r="BP10" s="3"/>
+    </row>
+    <row r="11" spans="1:68" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
         <v>21</v>
       </c>
@@ -1588,7 +1712,10 @@
       <c r="I11" s="11">
         <v>1636</v>
       </c>
-      <c r="J11" s="11"/>
+      <c r="J11" s="11">
+        <f t="shared" si="0"/>
+        <v>1712</v>
+      </c>
       <c r="K11" s="11">
         <v>1728</v>
       </c>
@@ -1598,25 +1725,30 @@
       <c r="M11" s="11">
         <v>2139</v>
       </c>
-      <c r="N11" s="11"/>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11">
-        <v>6456</v>
-      </c>
-      <c r="Q11" s="11">
-        <v>8091</v>
-      </c>
+      <c r="N11" s="11">
+        <f t="shared" si="1"/>
+        <v>2330</v>
+      </c>
+      <c r="O11" s="11">
+        <v>2397</v>
+      </c>
+      <c r="P11" s="11"/>
+      <c r="Q11" s="11"/>
       <c r="R11" s="11"/>
       <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="T11" s="11">
+        <v>6456</v>
+      </c>
+      <c r="U11" s="11">
+        <v>8091</v>
+      </c>
       <c r="V11" s="11"/>
       <c r="W11" s="11"/>
       <c r="X11" s="11"/>
-      <c r="Y11" s="3"/>
-      <c r="Z11" s="3"/>
-      <c r="AA11" s="3"/>
-      <c r="AB11" s="3"/>
+      <c r="Y11" s="11"/>
+      <c r="Z11" s="11"/>
+      <c r="AA11" s="11"/>
+      <c r="AB11" s="11"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
@@ -1653,8 +1785,12 @@
       <c r="BJ11" s="3"/>
       <c r="BK11" s="3"/>
       <c r="BL11" s="3"/>
-    </row>
-    <row r="12" spans="1:64" x14ac:dyDescent="0.2">
+      <c r="BM11" s="3"/>
+      <c r="BN11" s="3"/>
+      <c r="BO11" s="3"/>
+      <c r="BP11" s="3"/>
+    </row>
+    <row r="12" spans="1:68" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
         <v>22</v>
       </c>
@@ -1677,7 +1813,10 @@
       <c r="I12" s="11">
         <v>721</v>
       </c>
-      <c r="J12" s="11"/>
+      <c r="J12" s="11">
+        <f t="shared" si="0"/>
+        <v>767</v>
+      </c>
       <c r="K12" s="11">
         <v>886</v>
       </c>
@@ -1687,25 +1826,30 @@
       <c r="M12" s="11">
         <v>1069</v>
       </c>
-      <c r="N12" s="11"/>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11">
-        <v>2735</v>
-      </c>
-      <c r="Q12" s="11">
-        <v>4144</v>
-      </c>
+      <c r="N12" s="11">
+        <f t="shared" si="1"/>
+        <v>1198</v>
+      </c>
+      <c r="O12" s="11">
+        <v>1253</v>
+      </c>
+      <c r="P12" s="11"/>
+      <c r="Q12" s="11"/>
       <c r="R12" s="11"/>
       <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="T12" s="11">
+        <v>2735</v>
+      </c>
+      <c r="U12" s="11">
+        <v>4144</v>
+      </c>
       <c r="V12" s="11"/>
       <c r="W12" s="11"/>
       <c r="X12" s="11"/>
-      <c r="Y12" s="3"/>
-      <c r="Z12" s="3"/>
-      <c r="AA12" s="3"/>
-      <c r="AB12" s="3"/>
+      <c r="Y12" s="11"/>
+      <c r="Z12" s="11"/>
+      <c r="AA12" s="11"/>
+      <c r="AB12" s="11"/>
       <c r="AC12" s="3"/>
       <c r="AD12" s="3"/>
       <c r="AE12" s="3"/>
@@ -1742,8 +1886,12 @@
       <c r="BJ12" s="3"/>
       <c r="BK12" s="3"/>
       <c r="BL12" s="3"/>
-    </row>
-    <row r="13" spans="1:64" x14ac:dyDescent="0.2">
+      <c r="BM12" s="3"/>
+      <c r="BN12" s="3"/>
+      <c r="BO12" s="3"/>
+      <c r="BP12" s="3"/>
+    </row>
+    <row r="13" spans="1:68" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
         <v>19</v>
       </c>
@@ -1766,7 +1914,10 @@
       <c r="I13" s="11">
         <v>352</v>
       </c>
-      <c r="J13" s="11"/>
+      <c r="J13" s="11">
+        <f t="shared" si="0"/>
+        <v>332</v>
+      </c>
       <c r="K13" s="11">
         <v>316</v>
       </c>
@@ -1776,25 +1927,30 @@
       <c r="M13" s="11">
         <v>302</v>
       </c>
-      <c r="N13" s="11"/>
-      <c r="O13" s="11"/>
-      <c r="P13" s="11">
-        <v>1448</v>
-      </c>
-      <c r="Q13" s="11">
-        <v>1223</v>
-      </c>
+      <c r="N13" s="11">
+        <f t="shared" si="1"/>
+        <v>297</v>
+      </c>
+      <c r="O13" s="11">
+        <v>290</v>
+      </c>
+      <c r="P13" s="11"/>
+      <c r="Q13" s="11"/>
       <c r="R13" s="11"/>
       <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
+      <c r="T13" s="11">
+        <v>1448</v>
+      </c>
+      <c r="U13" s="11">
+        <v>1223</v>
+      </c>
       <c r="V13" s="11"/>
       <c r="W13" s="11"/>
       <c r="X13" s="11"/>
-      <c r="Y13" s="3"/>
-      <c r="Z13" s="3"/>
-      <c r="AA13" s="3"/>
-      <c r="AB13" s="3"/>
+      <c r="Y13" s="11"/>
+      <c r="Z13" s="11"/>
+      <c r="AA13" s="11"/>
+      <c r="AB13" s="11"/>
       <c r="AC13" s="3"/>
       <c r="AD13" s="3"/>
       <c r="AE13" s="3"/>
@@ -1831,8 +1987,12 @@
       <c r="BJ13" s="3"/>
       <c r="BK13" s="3"/>
       <c r="BL13" s="3"/>
-    </row>
-    <row r="14" spans="1:64" x14ac:dyDescent="0.2">
+      <c r="BM13" s="3"/>
+      <c r="BN13" s="3"/>
+      <c r="BO13" s="3"/>
+      <c r="BP13" s="3"/>
+    </row>
+    <row r="14" spans="1:68" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
         <v>23</v>
       </c>
@@ -1855,7 +2015,10 @@
       <c r="I14" s="11">
         <v>14</v>
       </c>
-      <c r="J14" s="11"/>
+      <c r="J14" s="11">
+        <f t="shared" si="0"/>
+        <v>-200</v>
+      </c>
       <c r="K14" s="11">
         <v>0</v>
       </c>
@@ -1865,25 +2028,30 @@
       <c r="M14" s="11">
         <v>0</v>
       </c>
-      <c r="N14" s="11"/>
-      <c r="O14" s="11"/>
-      <c r="P14" s="11">
-        <v>-186</v>
-      </c>
-      <c r="Q14" s="11">
+      <c r="N14" s="11">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
+      <c r="O14" s="11">
+        <v>0</v>
+      </c>
+      <c r="P14" s="11"/>
+      <c r="Q14" s="11"/>
       <c r="R14" s="11"/>
       <c r="S14" s="11"/>
-      <c r="T14" s="11"/>
-      <c r="U14" s="11"/>
+      <c r="T14" s="11">
+        <v>-186</v>
+      </c>
+      <c r="U14" s="11">
+        <v>0</v>
+      </c>
       <c r="V14" s="11"/>
       <c r="W14" s="11"/>
       <c r="X14" s="11"/>
-      <c r="Y14" s="3"/>
-      <c r="Z14" s="3"/>
-      <c r="AA14" s="3"/>
-      <c r="AB14" s="3"/>
+      <c r="Y14" s="11"/>
+      <c r="Z14" s="11"/>
+      <c r="AA14" s="11"/>
+      <c r="AB14" s="11"/>
       <c r="AC14" s="3"/>
       <c r="AD14" s="3"/>
       <c r="AE14" s="3"/>
@@ -1920,33 +2088,37 @@
       <c r="BJ14" s="3"/>
       <c r="BK14" s="3"/>
       <c r="BL14" s="3"/>
-    </row>
-    <row r="15" spans="1:64" x14ac:dyDescent="0.2">
+      <c r="BM14" s="3"/>
+      <c r="BN14" s="3"/>
+      <c r="BO14" s="3"/>
+      <c r="BP14" s="3"/>
+    </row>
+    <row r="15" spans="1:68" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C15" s="11">
-        <f t="shared" ref="C15:H15" si="2">+C10-SUM(C11:C13)+C14</f>
+        <f t="shared" ref="C15:H15" si="4">+C10-SUM(C11:C13)+C14</f>
         <v>-145</v>
       </c>
       <c r="D15" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-20</v>
       </c>
       <c r="E15" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>224</v>
       </c>
       <c r="F15" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G15" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>36</v>
       </c>
       <c r="H15" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>269</v>
       </c>
       <c r="I15" s="11">
@@ -1954,45 +2126,48 @@
         <v>724</v>
       </c>
       <c r="J15" s="11">
-        <f t="shared" ref="J15:Q15" si="3">+J10-SUM(J11:J13)+J14</f>
-        <v>0</v>
+        <f t="shared" ref="J15:U15" si="5">+J10-SUM(J11:J13)+J14</f>
+        <v>871</v>
       </c>
       <c r="K15" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>806</v>
       </c>
       <c r="L15" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>-134</v>
       </c>
       <c r="M15" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1270</v>
       </c>
       <c r="N15" s="11">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="O15" s="11"/>
-      <c r="P15" s="11">
-        <f t="shared" si="3"/>
-        <v>1900</v>
-      </c>
-      <c r="Q15" s="11">
-        <f t="shared" si="3"/>
-        <v>3694</v>
-      </c>
+        <f t="shared" si="5"/>
+        <v>1752</v>
+      </c>
+      <c r="O15" s="11">
+        <f t="shared" si="5"/>
+        <v>1476</v>
+      </c>
+      <c r="P15" s="11"/>
+      <c r="Q15" s="11"/>
       <c r="R15" s="11"/>
       <c r="S15" s="11"/>
-      <c r="T15" s="11"/>
-      <c r="U15" s="11"/>
+      <c r="T15" s="11">
+        <f t="shared" si="5"/>
+        <v>1900</v>
+      </c>
+      <c r="U15" s="11">
+        <f t="shared" si="5"/>
+        <v>3694</v>
+      </c>
       <c r="V15" s="11"/>
       <c r="W15" s="11"/>
       <c r="X15" s="11"/>
-      <c r="Y15" s="3"/>
-      <c r="Z15" s="3"/>
-      <c r="AA15" s="3"/>
-      <c r="AB15" s="3"/>
+      <c r="Y15" s="11"/>
+      <c r="Z15" s="11"/>
+      <c r="AA15" s="11"/>
+      <c r="AB15" s="11"/>
       <c r="AC15" s="3"/>
       <c r="AD15" s="3"/>
       <c r="AE15" s="3"/>
@@ -2029,8 +2204,12 @@
       <c r="BJ15" s="3"/>
       <c r="BK15" s="3"/>
       <c r="BL15" s="3"/>
-    </row>
-    <row r="16" spans="1:64" x14ac:dyDescent="0.2">
+      <c r="BM15" s="3"/>
+      <c r="BN15" s="3"/>
+      <c r="BO15" s="3"/>
+      <c r="BP15" s="3"/>
+    </row>
+    <row r="16" spans="1:68" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
         <v>25</v>
       </c>
@@ -2053,7 +2232,10 @@
       <c r="I16" s="11">
         <v>23</v>
       </c>
-      <c r="J16" s="11"/>
+      <c r="J16" s="11">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
       <c r="K16" s="11">
         <v>20</v>
       </c>
@@ -2063,25 +2245,30 @@
       <c r="M16" s="11">
         <v>37</v>
       </c>
-      <c r="N16" s="11"/>
-      <c r="O16" s="11"/>
-      <c r="P16" s="11">
-        <v>92</v>
-      </c>
-      <c r="Q16" s="11">
-        <v>131</v>
-      </c>
+      <c r="N16" s="11">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="O16" s="11">
+        <v>37</v>
+      </c>
+      <c r="P16" s="11"/>
+      <c r="Q16" s="11"/>
       <c r="R16" s="11"/>
       <c r="S16" s="11"/>
-      <c r="T16" s="11"/>
-      <c r="U16" s="11"/>
+      <c r="T16" s="11">
+        <v>92</v>
+      </c>
+      <c r="U16" s="11">
+        <v>131</v>
+      </c>
       <c r="V16" s="11"/>
       <c r="W16" s="11"/>
       <c r="X16" s="11"/>
-      <c r="Y16" s="3"/>
-      <c r="Z16" s="3"/>
-      <c r="AA16" s="3"/>
-      <c r="AB16" s="3"/>
+      <c r="Y16" s="11"/>
+      <c r="Z16" s="11"/>
+      <c r="AA16" s="11"/>
+      <c r="AB16" s="11"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
@@ -2118,8 +2305,12 @@
       <c r="BJ16" s="3"/>
       <c r="BK16" s="3"/>
       <c r="BL16" s="3"/>
-    </row>
-    <row r="17" spans="2:64" x14ac:dyDescent="0.2">
+      <c r="BM16" s="3"/>
+      <c r="BN16" s="3"/>
+      <c r="BO16" s="3"/>
+      <c r="BP16" s="3"/>
+    </row>
+    <row r="17" spans="2:68" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
         <v>26</v>
       </c>
@@ -2142,7 +2333,10 @@
       <c r="I17" s="11">
         <v>36</v>
       </c>
-      <c r="J17" s="11"/>
+      <c r="J17" s="11">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
       <c r="K17" s="11">
         <v>39</v>
       </c>
@@ -2152,25 +2346,30 @@
       <c r="M17" s="11">
         <v>82</v>
       </c>
-      <c r="N17" s="11"/>
-      <c r="O17" s="11"/>
-      <c r="P17" s="11">
-        <v>181</v>
-      </c>
-      <c r="Q17" s="11">
-        <v>577</v>
-      </c>
+      <c r="N17" s="11">
+        <f t="shared" si="1"/>
+        <v>358</v>
+      </c>
+      <c r="O17" s="11">
+        <v>165</v>
+      </c>
+      <c r="P17" s="11"/>
+      <c r="Q17" s="11"/>
       <c r="R17" s="11"/>
       <c r="S17" s="11"/>
-      <c r="T17" s="11"/>
-      <c r="U17" s="11"/>
+      <c r="T17" s="11">
+        <v>181</v>
+      </c>
+      <c r="U17" s="11">
+        <v>577</v>
+      </c>
       <c r="V17" s="11"/>
       <c r="W17" s="11"/>
       <c r="X17" s="11"/>
-      <c r="Y17" s="3"/>
-      <c r="Z17" s="3"/>
-      <c r="AA17" s="3"/>
-      <c r="AB17" s="3"/>
+      <c r="Y17" s="11"/>
+      <c r="Z17" s="11"/>
+      <c r="AA17" s="11"/>
+      <c r="AB17" s="11"/>
       <c r="AC17" s="3"/>
       <c r="AD17" s="3"/>
       <c r="AE17" s="3"/>
@@ -2207,33 +2406,37 @@
       <c r="BJ17" s="3"/>
       <c r="BK17" s="3"/>
       <c r="BL17" s="3"/>
-    </row>
-    <row r="18" spans="2:64" x14ac:dyDescent="0.2">
+      <c r="BM17" s="3"/>
+      <c r="BN17" s="3"/>
+      <c r="BO17" s="3"/>
+      <c r="BP17" s="3"/>
+    </row>
+    <row r="18" spans="2:68" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C18" s="11">
-        <f t="shared" ref="C18:H18" si="4">+C15-C16+C17</f>
+        <f t="shared" ref="C18:H18" si="6">+C15-C16+C17</f>
         <v>-127</v>
       </c>
       <c r="D18" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>-2</v>
       </c>
       <c r="E18" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>257</v>
       </c>
       <c r="F18" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="G18" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>64</v>
       </c>
       <c r="H18" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>299</v>
       </c>
       <c r="I18" s="11">
@@ -2241,45 +2444,48 @@
         <v>737</v>
       </c>
       <c r="J18" s="11">
-        <f t="shared" ref="J18:Q18" si="5">+J15-J16+J17</f>
-        <v>0</v>
+        <f t="shared" ref="J18:U18" si="7">+J15-J16+J17</f>
+        <v>889</v>
       </c>
       <c r="K18" s="11">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>825</v>
       </c>
       <c r="L18" s="11">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>-74</v>
       </c>
       <c r="M18" s="11">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1315</v>
       </c>
       <c r="N18" s="11">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="O18" s="11"/>
-      <c r="P18" s="11">
-        <f t="shared" si="5"/>
-        <v>1989</v>
-      </c>
-      <c r="Q18" s="11">
-        <f t="shared" si="5"/>
-        <v>4140</v>
-      </c>
+        <f t="shared" si="7"/>
+        <v>2074</v>
+      </c>
+      <c r="O18" s="11">
+        <f t="shared" si="7"/>
+        <v>1604</v>
+      </c>
+      <c r="P18" s="11"/>
+      <c r="Q18" s="11"/>
       <c r="R18" s="11"/>
       <c r="S18" s="11"/>
-      <c r="T18" s="11"/>
-      <c r="U18" s="11"/>
+      <c r="T18" s="11">
+        <f t="shared" si="7"/>
+        <v>1989</v>
+      </c>
+      <c r="U18" s="11">
+        <f t="shared" si="7"/>
+        <v>4140</v>
+      </c>
       <c r="V18" s="11"/>
       <c r="W18" s="11"/>
       <c r="X18" s="11"/>
-      <c r="Y18" s="3"/>
-      <c r="Z18" s="3"/>
-      <c r="AA18" s="3"/>
-      <c r="AB18" s="3"/>
+      <c r="Y18" s="11"/>
+      <c r="Z18" s="11"/>
+      <c r="AA18" s="11"/>
+      <c r="AB18" s="11"/>
       <c r="AC18" s="3"/>
       <c r="AD18" s="3"/>
       <c r="AE18" s="3"/>
@@ -2316,8 +2522,12 @@
       <c r="BJ18" s="3"/>
       <c r="BK18" s="3"/>
       <c r="BL18" s="3"/>
-    </row>
-    <row r="19" spans="2:64" x14ac:dyDescent="0.2">
+      <c r="BM18" s="3"/>
+      <c r="BN18" s="3"/>
+      <c r="BO18" s="3"/>
+      <c r="BP18" s="3"/>
+    </row>
+    <row r="19" spans="2:68" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
         <v>28</v>
       </c>
@@ -2340,7 +2550,10 @@
       <c r="I19" s="11">
         <v>-27</v>
       </c>
-      <c r="J19" s="11"/>
+      <c r="J19" s="11">
+        <f t="shared" si="0"/>
+        <v>419</v>
+      </c>
       <c r="K19" s="11">
         <v>123</v>
       </c>
@@ -2350,25 +2563,30 @@
       <c r="M19" s="11">
         <v>153</v>
       </c>
-      <c r="N19" s="11"/>
-      <c r="O19" s="11"/>
-      <c r="P19" s="11">
-        <v>381</v>
-      </c>
-      <c r="Q19" s="11">
-        <v>-103</v>
-      </c>
+      <c r="N19" s="11">
+        <f t="shared" si="1"/>
+        <v>455</v>
+      </c>
+      <c r="O19" s="11">
+        <v>238</v>
+      </c>
+      <c r="P19" s="11"/>
+      <c r="Q19" s="11"/>
       <c r="R19" s="11"/>
       <c r="S19" s="11"/>
-      <c r="T19" s="11"/>
-      <c r="U19" s="11"/>
+      <c r="T19" s="11">
+        <v>381</v>
+      </c>
+      <c r="U19" s="11">
+        <v>-103</v>
+      </c>
       <c r="V19" s="11"/>
       <c r="W19" s="11"/>
       <c r="X19" s="11"/>
-      <c r="Y19" s="3"/>
-      <c r="Z19" s="3"/>
-      <c r="AA19" s="3"/>
-      <c r="AB19" s="3"/>
+      <c r="Y19" s="11"/>
+      <c r="Z19" s="11"/>
+      <c r="AA19" s="11"/>
+      <c r="AB19" s="11"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
@@ -2405,8 +2623,12 @@
       <c r="BJ19" s="3"/>
       <c r="BK19" s="3"/>
       <c r="BL19" s="3"/>
-    </row>
-    <row r="20" spans="2:64" x14ac:dyDescent="0.2">
+      <c r="BM19" s="3"/>
+      <c r="BN19" s="3"/>
+      <c r="BO19" s="3"/>
+      <c r="BP19" s="3"/>
+    </row>
+    <row r="20" spans="2:68" x14ac:dyDescent="0.2">
       <c r="B20" s="9" t="s">
         <v>39</v>
       </c>
@@ -2429,7 +2651,10 @@
       <c r="I20" s="11">
         <v>7</v>
       </c>
-      <c r="J20" s="11"/>
+      <c r="J20" s="11">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
       <c r="K20" s="11">
         <v>7</v>
       </c>
@@ -2441,26 +2666,32 @@
         <f>10+71</f>
         <v>81</v>
       </c>
-      <c r="N20" s="11"/>
-      <c r="O20" s="11"/>
-      <c r="P20" s="11">
+      <c r="N20" s="11">
+        <f t="shared" si="1"/>
+        <v>-108</v>
+      </c>
+      <c r="O20" s="11">
+        <f>6+11</f>
+        <v>17</v>
+      </c>
+      <c r="P20" s="11"/>
+      <c r="Q20" s="11"/>
+      <c r="R20" s="11"/>
+      <c r="S20" s="11"/>
+      <c r="T20" s="11">
         <v>33</v>
       </c>
-      <c r="Q20" s="11">
+      <c r="U20" s="11">
         <f>26+66</f>
         <v>92</v>
       </c>
-      <c r="R20" s="11"/>
-      <c r="S20" s="11"/>
-      <c r="T20" s="11"/>
-      <c r="U20" s="11"/>
       <c r="V20" s="11"/>
       <c r="W20" s="11"/>
       <c r="X20" s="11"/>
-      <c r="Y20" s="3"/>
-      <c r="Z20" s="3"/>
-      <c r="AA20" s="3"/>
-      <c r="AB20" s="3"/>
+      <c r="Y20" s="11"/>
+      <c r="Z20" s="11"/>
+      <c r="AA20" s="11"/>
+      <c r="AB20" s="11"/>
       <c r="AC20" s="3"/>
       <c r="AD20" s="3"/>
       <c r="AE20" s="3"/>
@@ -2497,33 +2728,37 @@
       <c r="BJ20" s="3"/>
       <c r="BK20" s="3"/>
       <c r="BL20" s="3"/>
-    </row>
-    <row r="21" spans="2:64" x14ac:dyDescent="0.2">
+      <c r="BM20" s="3"/>
+      <c r="BN20" s="3"/>
+      <c r="BO20" s="3"/>
+      <c r="BP20" s="3"/>
+    </row>
+    <row r="21" spans="2:68" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C21" s="11">
-        <f t="shared" ref="C21:H21" si="6">+C18-C19+C20</f>
+        <f t="shared" ref="C21:H21" si="8">+C18-C19+C20</f>
         <v>-139</v>
       </c>
       <c r="D21" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>27</v>
       </c>
       <c r="E21" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>299</v>
       </c>
       <c r="F21" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="G21" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>123</v>
       </c>
       <c r="H21" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>265</v>
       </c>
       <c r="I21" s="11">
@@ -2531,45 +2766,48 @@
         <v>771</v>
       </c>
       <c r="J21" s="11">
-        <f t="shared" ref="J21:Q21" si="7">+J18-J19+J20</f>
-        <v>0</v>
+        <f t="shared" ref="J21:U21" si="9">+J18-J19+J20</f>
+        <v>482</v>
       </c>
       <c r="K21" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>709</v>
       </c>
       <c r="L21" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>872</v>
       </c>
       <c r="M21" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>1243</v>
       </c>
       <c r="N21" s="11">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="O21" s="11"/>
-      <c r="P21" s="11">
-        <f t="shared" si="7"/>
-        <v>1641</v>
-      </c>
-      <c r="Q21" s="11">
-        <f t="shared" si="7"/>
-        <v>4335</v>
-      </c>
+        <f t="shared" si="9"/>
+        <v>1511</v>
+      </c>
+      <c r="O21" s="11">
+        <f t="shared" si="9"/>
+        <v>1383</v>
+      </c>
+      <c r="P21" s="11"/>
+      <c r="Q21" s="11"/>
       <c r="R21" s="11"/>
       <c r="S21" s="11"/>
-      <c r="T21" s="11"/>
-      <c r="U21" s="11"/>
+      <c r="T21" s="11">
+        <f t="shared" si="9"/>
+        <v>1641</v>
+      </c>
+      <c r="U21" s="11">
+        <f t="shared" si="9"/>
+        <v>4335</v>
+      </c>
       <c r="V21" s="11"/>
       <c r="W21" s="11"/>
       <c r="X21" s="11"/>
-      <c r="Y21" s="3"/>
-      <c r="Z21" s="3"/>
-      <c r="AA21" s="3"/>
-      <c r="AB21" s="3"/>
+      <c r="Y21" s="11"/>
+      <c r="Z21" s="11"/>
+      <c r="AA21" s="11"/>
+      <c r="AB21" s="11"/>
       <c r="AC21" s="3"/>
       <c r="AD21" s="3"/>
       <c r="AE21" s="3"/>
@@ -2606,8 +2844,12 @@
       <c r="BJ21" s="3"/>
       <c r="BK21" s="3"/>
       <c r="BL21" s="3"/>
-    </row>
-    <row r="22" spans="2:64" x14ac:dyDescent="0.2">
+      <c r="BM21" s="3"/>
+      <c r="BN21" s="3"/>
+      <c r="BO21" s="3"/>
+      <c r="BP21" s="3"/>
+    </row>
+    <row r="22" spans="2:68" x14ac:dyDescent="0.2">
       <c r="C22" s="11"/>
       <c r="D22" s="11"/>
       <c r="E22" s="11"/>
@@ -2630,10 +2872,10 @@
       <c r="V22" s="11"/>
       <c r="W22" s="11"/>
       <c r="X22" s="11"/>
-      <c r="Y22" s="3"/>
-      <c r="Z22" s="3"/>
-      <c r="AA22" s="3"/>
-      <c r="AB22" s="3"/>
+      <c r="Y22" s="11"/>
+      <c r="Z22" s="11"/>
+      <c r="AA22" s="11"/>
+      <c r="AB22" s="11"/>
       <c r="AC22" s="3"/>
       <c r="AD22" s="3"/>
       <c r="AE22" s="3"/>
@@ -2670,72 +2912,79 @@
       <c r="BJ22" s="3"/>
       <c r="BK22" s="3"/>
       <c r="BL22" s="3"/>
-    </row>
-    <row r="23" spans="2:64" x14ac:dyDescent="0.2">
+      <c r="BM22" s="3"/>
+      <c r="BN22" s="3"/>
+      <c r="BO22" s="3"/>
+      <c r="BP22" s="3"/>
+    </row>
+    <row r="23" spans="2:68" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C23" s="7">
-        <f t="shared" ref="C23:H23" si="8">+C21/C24</f>
+        <f t="shared" ref="C23:H23" si="10">+C21/C24</f>
         <v>-8.6281812538795785E-2</v>
       </c>
       <c r="D23" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1.6749379652605458E-2</v>
       </c>
       <c r="E23" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0.18502475247524752</v>
       </c>
       <c r="F23" s="7" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G23" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>7.6066790352504632E-2</v>
       </c>
       <c r="H23" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0.16378244746600742</v>
       </c>
       <c r="I23" s="7">
         <f>+I21/I24</f>
         <v>0.47592592592592592</v>
       </c>
-      <c r="J23" s="7" t="e">
-        <f t="shared" ref="J23:Q23" si="9">+J21/J24</f>
-        <v>#DIV/0!</v>
+      <c r="J23" s="7">
+        <f t="shared" ref="J23:U23" si="11">+J21/J24</f>
+        <v>0.29753086419753089</v>
       </c>
       <c r="K23" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0.43765432098765433</v>
       </c>
       <c r="L23" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0.5372766481823783</v>
       </c>
       <c r="M23" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0.76445264452644524</v>
       </c>
-      <c r="N23" s="7" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O23" s="3"/>
-      <c r="P23" s="7">
-        <f t="shared" si="9"/>
+      <c r="N23" s="7">
+        <f t="shared" si="11"/>
+        <v>0.93041871921182262</v>
+      </c>
+      <c r="O23" s="7">
+        <f t="shared" si="11"/>
+        <v>0.8479460453709381</v>
+      </c>
+      <c r="P23" s="7"/>
+      <c r="Q23" s="7"/>
+      <c r="R23" s="7"/>
+      <c r="S23" s="3"/>
+      <c r="T23" s="7">
+        <f t="shared" si="11"/>
         <v>1.0129629629629631</v>
       </c>
-      <c r="Q23" s="7">
-        <f t="shared" si="9"/>
+      <c r="U23" s="7">
+        <f t="shared" si="11"/>
         <v>2.6693349753694582</v>
       </c>
-      <c r="R23" s="3"/>
-      <c r="S23" s="3"/>
-      <c r="T23" s="3"/>
-      <c r="U23" s="3"/>
       <c r="V23" s="3"/>
       <c r="W23" s="3"/>
       <c r="X23" s="3"/>
@@ -2779,8 +3028,12 @@
       <c r="BJ23" s="3"/>
       <c r="BK23" s="3"/>
       <c r="BL23" s="3"/>
-    </row>
-    <row r="24" spans="2:64" x14ac:dyDescent="0.2">
+      <c r="BM23" s="3"/>
+      <c r="BN23" s="3"/>
+      <c r="BO23" s="3"/>
+      <c r="BP23" s="3"/>
+    </row>
+    <row r="24" spans="2:68" x14ac:dyDescent="0.2">
       <c r="B24" s="2" t="s">
         <v>2</v>
       </c>
@@ -2803,7 +3056,9 @@
       <c r="I24" s="3">
         <v>1620</v>
       </c>
-      <c r="J24" s="3"/>
+      <c r="J24" s="3">
+        <v>1620</v>
+      </c>
       <c r="K24" s="3">
         <v>1620</v>
       </c>
@@ -2813,18 +3068,22 @@
       <c r="M24" s="3">
         <v>1626</v>
       </c>
-      <c r="N24" s="3"/>
-      <c r="O24" s="3"/>
-      <c r="P24" s="3">
-        <v>1620</v>
-      </c>
-      <c r="Q24" s="3">
+      <c r="N24" s="3">
         <v>1624</v>
       </c>
+      <c r="O24" s="3">
+        <v>1631</v>
+      </c>
+      <c r="P24" s="3"/>
+      <c r="Q24" s="3"/>
       <c r="R24" s="3"/>
       <c r="S24" s="3"/>
-      <c r="T24" s="3"/>
-      <c r="U24" s="3"/>
+      <c r="T24" s="3">
+        <v>1620</v>
+      </c>
+      <c r="U24" s="3">
+        <v>1624</v>
+      </c>
       <c r="V24" s="3"/>
       <c r="W24" s="3"/>
       <c r="X24" s="3"/>
@@ -2868,8 +3127,12 @@
       <c r="BJ24" s="3"/>
       <c r="BK24" s="3"/>
       <c r="BL24" s="3"/>
-    </row>
-    <row r="25" spans="2:64" x14ac:dyDescent="0.2">
+      <c r="BM24" s="3"/>
+      <c r="BN24" s="3"/>
+      <c r="BO24" s="3"/>
+      <c r="BP24" s="3"/>
+    </row>
+    <row r="25" spans="2:68" x14ac:dyDescent="0.2">
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
@@ -2932,8 +3195,12 @@
       <c r="BJ25" s="3"/>
       <c r="BK25" s="3"/>
       <c r="BL25" s="3"/>
-    </row>
-    <row r="26" spans="2:64" x14ac:dyDescent="0.2">
+      <c r="BM25" s="3"/>
+      <c r="BN25" s="3"/>
+      <c r="BO25" s="3"/>
+      <c r="BP25" s="3"/>
+    </row>
+    <row r="26" spans="2:68" x14ac:dyDescent="0.2">
       <c r="B26" s="1" t="s">
         <v>31</v>
       </c>
@@ -2942,11 +3209,11 @@
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
       <c r="G26" s="13">
-        <f t="shared" ref="G26:H26" si="10">+G7/C7-1</f>
+        <f t="shared" ref="G26:H26" si="12">+G7/C7-1</f>
         <v>2.2417336073230043E-2</v>
       </c>
       <c r="H26" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>8.882254151894009E-2</v>
       </c>
       <c r="I26" s="13">
@@ -2954,35 +3221,38 @@
         <v>0.17568965517241386</v>
       </c>
       <c r="J26" s="13" t="e">
-        <f t="shared" ref="J26:N26" si="11">+J7/F7-1</f>
+        <f t="shared" ref="J26:O26" si="13">+J7/F7-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K26" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.35903526402338759</v>
       </c>
       <c r="L26" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.31705227077977716</v>
       </c>
       <c r="M26" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.35591728992520899</v>
       </c>
-      <c r="N26" s="13" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O26" s="3"/>
-      <c r="P26" s="3"/>
-      <c r="Q26" s="13">
-        <f>+Q7/P7-1</f>
-        <v>0.3433779329067288</v>
-      </c>
-      <c r="R26" s="3"/>
+      <c r="N26" s="13">
+        <f t="shared" si="13"/>
+        <v>0.34108122225124049</v>
+      </c>
+      <c r="O26" s="13">
+        <f t="shared" si="13"/>
+        <v>0.37846195213767131</v>
+      </c>
+      <c r="P26" s="13"/>
+      <c r="Q26" s="13"/>
+      <c r="R26" s="13"/>
       <c r="S26" s="3"/>
       <c r="T26" s="3"/>
-      <c r="U26" s="3"/>
+      <c r="U26" s="13">
+        <f>+U7/T7-1</f>
+        <v>0.3433779329067288</v>
+      </c>
       <c r="V26" s="3"/>
       <c r="W26" s="3"/>
       <c r="X26" s="3"/>
@@ -3026,72 +3296,79 @@
       <c r="BJ26" s="3"/>
       <c r="BK26" s="3"/>
       <c r="BL26" s="3"/>
-    </row>
-    <row r="27" spans="2:64" x14ac:dyDescent="0.2">
+      <c r="BM26" s="3"/>
+      <c r="BN26" s="3"/>
+      <c r="BO26" s="3"/>
+      <c r="BP26" s="3"/>
+    </row>
+    <row r="27" spans="2:68" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C27" s="8">
-        <f t="shared" ref="C27:H27" si="12">+C10/C7</f>
+        <f t="shared" ref="C27:H27" si="14">+C10/C7</f>
         <v>0.44068746497291239</v>
       </c>
       <c r="D27" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.4558686322075014</v>
       </c>
       <c r="E27" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.4736206896551724</v>
       </c>
       <c r="F27" s="8" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G27" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.46775077653937513</v>
       </c>
       <c r="H27" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.49083119108826051</v>
       </c>
       <c r="I27" s="8">
         <f>+I10/I7</f>
         <v>0.50139316615339491</v>
       </c>
-      <c r="J27" s="8" t="e">
-        <f t="shared" ref="J27:N27" si="13">+J10/J7</f>
-        <v>#DIV/0!</v>
+      <c r="J27" s="8">
+        <f t="shared" ref="J27:N27" si="15">+J10/J7</f>
+        <v>0.50692086706711936</v>
       </c>
       <c r="K27" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.50228556063457919</v>
       </c>
       <c r="L27" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.39804814573845154</v>
       </c>
       <c r="M27" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.51698031581224313</v>
       </c>
-      <c r="N27" s="8" t="e">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O27" s="3"/>
-      <c r="P27" s="8">
-        <f t="shared" ref="P27:Q27" si="14">+P10/P7</f>
+      <c r="N27" s="8">
+        <f t="shared" si="15"/>
+        <v>0.54303797468354431</v>
+      </c>
+      <c r="O27" s="8">
+        <f t="shared" ref="O27" si="16">+O10/O7</f>
+        <v>0.52823563834975129</v>
+      </c>
+      <c r="P27" s="8"/>
+      <c r="Q27" s="8"/>
+      <c r="R27" s="8"/>
+      <c r="S27" s="3"/>
+      <c r="T27" s="8">
+        <f t="shared" ref="T27:U27" si="17">+T10/T7</f>
         <v>0.49350397517936784</v>
       </c>
-      <c r="Q27" s="8">
-        <f t="shared" si="14"/>
+      <c r="U27" s="8">
+        <f t="shared" si="17"/>
         <v>0.49516441005802708</v>
       </c>
-      <c r="R27" s="3"/>
-      <c r="S27" s="3"/>
-      <c r="T27" s="3"/>
-      <c r="U27" s="3"/>
       <c r="V27" s="3"/>
       <c r="W27" s="3"/>
       <c r="X27" s="3"/>
@@ -3135,72 +3412,79 @@
       <c r="BJ27" s="3"/>
       <c r="BK27" s="3"/>
       <c r="BL27" s="3"/>
-    </row>
-    <row r="28" spans="2:64" x14ac:dyDescent="0.2">
+      <c r="BM27" s="3"/>
+      <c r="BN27" s="3"/>
+      <c r="BO27" s="3"/>
+      <c r="BP27" s="3"/>
+    </row>
+    <row r="28" spans="2:68" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C28" s="8">
-        <f t="shared" ref="C28:H28" si="15">+C15/C7</f>
+        <f t="shared" ref="C28:H28" si="18">+C15/C7</f>
         <v>-2.7087614421819541E-2</v>
       </c>
       <c r="D28" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>-3.7320395596193321E-3</v>
       </c>
       <c r="E28" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>3.8620689655172416E-2</v>
       </c>
       <c r="F28" s="8" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G28" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>6.5777452950849628E-3</v>
       </c>
       <c r="H28" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>4.6101113967437872E-2</v>
       </c>
       <c r="I28" s="8">
         <f>+I15/I7</f>
         <v>0.10617392579557119</v>
       </c>
-      <c r="J28" s="8" t="e">
-        <f t="shared" ref="J28:N28" si="16">+J15/J7</f>
-        <v>#DIV/0!</v>
+      <c r="J28" s="8">
+        <f t="shared" ref="J28:N28" si="19">+J15/J7</f>
+        <v>0.11373726821624446</v>
       </c>
       <c r="K28" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0.10836246302769562</v>
       </c>
       <c r="L28" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>-1.7436564736499675E-2</v>
       </c>
       <c r="M28" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0.13735669478693488</v>
       </c>
-      <c r="N28" s="8" t="e">
-        <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O28" s="3"/>
-      <c r="P28" s="8">
-        <f t="shared" ref="P28:Q28" si="17">+P15/P7</f>
+      <c r="N28" s="8">
+        <f t="shared" si="19"/>
+        <v>0.17059396299902629</v>
+      </c>
+      <c r="O28" s="8">
+        <f t="shared" ref="O28" si="20">+O15/O7</f>
+        <v>0.14395786599044183</v>
+      </c>
+      <c r="P28" s="8"/>
+      <c r="Q28" s="8"/>
+      <c r="R28" s="8"/>
+      <c r="S28" s="3"/>
+      <c r="T28" s="8">
+        <f t="shared" ref="T28:U28" si="21">+T15/T7</f>
         <v>7.3686251696722896E-2</v>
       </c>
-      <c r="Q28" s="8">
-        <f t="shared" si="17"/>
+      <c r="U28" s="8">
+        <f t="shared" si="21"/>
         <v>0.10664280146655504</v>
       </c>
-      <c r="R28" s="3"/>
-      <c r="S28" s="3"/>
-      <c r="T28" s="3"/>
-      <c r="U28" s="3"/>
       <c r="V28" s="3"/>
       <c r="W28" s="3"/>
       <c r="X28" s="3"/>
@@ -3244,72 +3528,79 @@
       <c r="BJ28" s="3"/>
       <c r="BK28" s="3"/>
       <c r="BL28" s="3"/>
-    </row>
-    <row r="29" spans="2:64" x14ac:dyDescent="0.2">
+      <c r="BM28" s="3"/>
+      <c r="BN28" s="3"/>
+      <c r="BO28" s="3"/>
+      <c r="BP28" s="3"/>
+    </row>
+    <row r="29" spans="2:68" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C29" s="8">
-        <f t="shared" ref="C29:H29" si="18">+C19/C18</f>
+        <f t="shared" ref="C29:H29" si="22">+C19/C18</f>
         <v>-0.10236220472440945</v>
       </c>
       <c r="D29" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>11.5</v>
       </c>
       <c r="E29" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>-0.1517509727626459</v>
       </c>
       <c r="F29" s="8" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G29" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>-0.8125</v>
       </c>
       <c r="H29" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0.13712374581939799</v>
       </c>
       <c r="I29" s="8">
         <f>+I19/I18</f>
         <v>-3.6635006784260515E-2</v>
       </c>
-      <c r="J29" s="8" t="e">
-        <f t="shared" ref="J29:N29" si="19">+J19/J18</f>
-        <v>#DIV/0!</v>
+      <c r="J29" s="8">
+        <f t="shared" ref="J29:N29" si="23">+J19/J18</f>
+        <v>0.47131608548931386</v>
       </c>
       <c r="K29" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>0.14909090909090908</v>
       </c>
       <c r="L29" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>11.27027027027027</v>
       </c>
       <c r="M29" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>0.11634980988593156</v>
       </c>
-      <c r="N29" s="8" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O29" s="3"/>
-      <c r="P29" s="8">
-        <f t="shared" ref="P29:Q29" si="20">+P19/P18</f>
+      <c r="N29" s="8">
+        <f t="shared" si="23"/>
+        <v>0.21938283510125361</v>
+      </c>
+      <c r="O29" s="8">
+        <f t="shared" ref="O29" si="24">+O19/O18</f>
+        <v>0.14837905236907731</v>
+      </c>
+      <c r="P29" s="8"/>
+      <c r="Q29" s="8"/>
+      <c r="R29" s="8"/>
+      <c r="S29" s="3"/>
+      <c r="T29" s="8">
+        <f t="shared" ref="T29:U29" si="25">+T19/T18</f>
         <v>0.19155354449472098</v>
       </c>
-      <c r="Q29" s="8">
-        <f t="shared" si="20"/>
+      <c r="U29" s="8">
+        <f t="shared" si="25"/>
         <v>-2.4879227053140097E-2</v>
       </c>
-      <c r="R29" s="3"/>
-      <c r="S29" s="3"/>
-      <c r="T29" s="3"/>
-      <c r="U29" s="3"/>
       <c r="V29" s="3"/>
       <c r="W29" s="3"/>
       <c r="X29" s="3"/>
@@ -3353,8 +3644,12 @@
       <c r="BJ29" s="3"/>
       <c r="BK29" s="3"/>
       <c r="BL29" s="3"/>
-    </row>
-    <row r="30" spans="2:64" x14ac:dyDescent="0.2">
+      <c r="BM29" s="3"/>
+      <c r="BN29" s="3"/>
+      <c r="BO29" s="3"/>
+      <c r="BP29" s="3"/>
+    </row>
+    <row r="30" spans="2:68" x14ac:dyDescent="0.2">
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
@@ -3417,8 +3712,12 @@
       <c r="BJ30" s="3"/>
       <c r="BK30" s="3"/>
       <c r="BL30" s="3"/>
-    </row>
-    <row r="31" spans="2:64" x14ac:dyDescent="0.2">
+      <c r="BM30" s="3"/>
+      <c r="BN30" s="3"/>
+      <c r="BO30" s="3"/>
+      <c r="BP30" s="3"/>
+    </row>
+    <row r="31" spans="2:68" x14ac:dyDescent="0.2">
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
@@ -3481,8 +3780,12 @@
       <c r="BJ31" s="3"/>
       <c r="BK31" s="3"/>
       <c r="BL31" s="3"/>
-    </row>
-    <row r="32" spans="2:64" x14ac:dyDescent="0.2">
+      <c r="BM31" s="3"/>
+      <c r="BN31" s="3"/>
+      <c r="BO31" s="3"/>
+      <c r="BP31" s="3"/>
+    </row>
+    <row r="32" spans="2:68" x14ac:dyDescent="0.2">
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
@@ -3545,8 +3848,12 @@
       <c r="BJ32" s="3"/>
       <c r="BK32" s="3"/>
       <c r="BL32" s="3"/>
-    </row>
-    <row r="33" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM32" s="3"/>
+      <c r="BN32" s="3"/>
+      <c r="BO32" s="3"/>
+      <c r="BP32" s="3"/>
+    </row>
+    <row r="33" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
@@ -3609,8 +3916,12 @@
       <c r="BJ33" s="3"/>
       <c r="BK33" s="3"/>
       <c r="BL33" s="3"/>
-    </row>
-    <row r="34" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM33" s="3"/>
+      <c r="BN33" s="3"/>
+      <c r="BO33" s="3"/>
+      <c r="BP33" s="3"/>
+    </row>
+    <row r="34" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
@@ -3673,8 +3984,12 @@
       <c r="BJ34" s="3"/>
       <c r="BK34" s="3"/>
       <c r="BL34" s="3"/>
-    </row>
-    <row r="35" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM34" s="3"/>
+      <c r="BN34" s="3"/>
+      <c r="BO34" s="3"/>
+      <c r="BP34" s="3"/>
+    </row>
+    <row r="35" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
@@ -3737,8 +4052,12 @@
       <c r="BJ35" s="3"/>
       <c r="BK35" s="3"/>
       <c r="BL35" s="3"/>
-    </row>
-    <row r="36" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM35" s="3"/>
+      <c r="BN35" s="3"/>
+      <c r="BO35" s="3"/>
+      <c r="BP35" s="3"/>
+    </row>
+    <row r="36" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
@@ -3801,8 +4120,12 @@
       <c r="BJ36" s="3"/>
       <c r="BK36" s="3"/>
       <c r="BL36" s="3"/>
-    </row>
-    <row r="37" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM36" s="3"/>
+      <c r="BN36" s="3"/>
+      <c r="BO36" s="3"/>
+      <c r="BP36" s="3"/>
+    </row>
+    <row r="37" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
@@ -3865,8 +4188,12 @@
       <c r="BJ37" s="3"/>
       <c r="BK37" s="3"/>
       <c r="BL37" s="3"/>
-    </row>
-    <row r="38" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM37" s="3"/>
+      <c r="BN37" s="3"/>
+      <c r="BO37" s="3"/>
+      <c r="BP37" s="3"/>
+    </row>
+    <row r="38" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
@@ -3929,8 +4256,12 @@
       <c r="BJ38" s="3"/>
       <c r="BK38" s="3"/>
       <c r="BL38" s="3"/>
-    </row>
-    <row r="39" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM38" s="3"/>
+      <c r="BN38" s="3"/>
+      <c r="BO38" s="3"/>
+      <c r="BP38" s="3"/>
+    </row>
+    <row r="39" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
@@ -3993,8 +4324,12 @@
       <c r="BJ39" s="3"/>
       <c r="BK39" s="3"/>
       <c r="BL39" s="3"/>
-    </row>
-    <row r="40" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM39" s="3"/>
+      <c r="BN39" s="3"/>
+      <c r="BO39" s="3"/>
+      <c r="BP39" s="3"/>
+    </row>
+    <row r="40" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
@@ -4057,8 +4392,12 @@
       <c r="BJ40" s="3"/>
       <c r="BK40" s="3"/>
       <c r="BL40" s="3"/>
-    </row>
-    <row r="41" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM40" s="3"/>
+      <c r="BN40" s="3"/>
+      <c r="BO40" s="3"/>
+      <c r="BP40" s="3"/>
+    </row>
+    <row r="41" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
@@ -4121,8 +4460,12 @@
       <c r="BJ41" s="3"/>
       <c r="BK41" s="3"/>
       <c r="BL41" s="3"/>
-    </row>
-    <row r="42" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM41" s="3"/>
+      <c r="BN41" s="3"/>
+      <c r="BO41" s="3"/>
+      <c r="BP41" s="3"/>
+    </row>
+    <row r="42" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
@@ -4185,8 +4528,12 @@
       <c r="BJ42" s="3"/>
       <c r="BK42" s="3"/>
       <c r="BL42" s="3"/>
-    </row>
-    <row r="43" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM42" s="3"/>
+      <c r="BN42" s="3"/>
+      <c r="BO42" s="3"/>
+      <c r="BP42" s="3"/>
+    </row>
+    <row r="43" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
@@ -4249,8 +4596,12 @@
       <c r="BJ43" s="3"/>
       <c r="BK43" s="3"/>
       <c r="BL43" s="3"/>
-    </row>
-    <row r="44" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM43" s="3"/>
+      <c r="BN43" s="3"/>
+      <c r="BO43" s="3"/>
+      <c r="BP43" s="3"/>
+    </row>
+    <row r="44" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
@@ -4313,8 +4664,12 @@
       <c r="BJ44" s="3"/>
       <c r="BK44" s="3"/>
       <c r="BL44" s="3"/>
-    </row>
-    <row r="45" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM44" s="3"/>
+      <c r="BN44" s="3"/>
+      <c r="BO44" s="3"/>
+      <c r="BP44" s="3"/>
+    </row>
+    <row r="45" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -4377,8 +4732,12 @@
       <c r="BJ45" s="3"/>
       <c r="BK45" s="3"/>
       <c r="BL45" s="3"/>
-    </row>
-    <row r="46" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM45" s="3"/>
+      <c r="BN45" s="3"/>
+      <c r="BO45" s="3"/>
+      <c r="BP45" s="3"/>
+    </row>
+    <row r="46" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
@@ -4441,8 +4800,12 @@
       <c r="BJ46" s="3"/>
       <c r="BK46" s="3"/>
       <c r="BL46" s="3"/>
-    </row>
-    <row r="47" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM46" s="3"/>
+      <c r="BN46" s="3"/>
+      <c r="BO46" s="3"/>
+      <c r="BP46" s="3"/>
+    </row>
+    <row r="47" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
@@ -4505,8 +4868,12 @@
       <c r="BJ47" s="3"/>
       <c r="BK47" s="3"/>
       <c r="BL47" s="3"/>
-    </row>
-    <row r="48" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM47" s="3"/>
+      <c r="BN47" s="3"/>
+      <c r="BO47" s="3"/>
+      <c r="BP47" s="3"/>
+    </row>
+    <row r="48" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
@@ -4569,8 +4936,12 @@
       <c r="BJ48" s="3"/>
       <c r="BK48" s="3"/>
       <c r="BL48" s="3"/>
-    </row>
-    <row r="49" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM48" s="3"/>
+      <c r="BN48" s="3"/>
+      <c r="BO48" s="3"/>
+      <c r="BP48" s="3"/>
+    </row>
+    <row r="49" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
@@ -4633,8 +5004,12 @@
       <c r="BJ49" s="3"/>
       <c r="BK49" s="3"/>
       <c r="BL49" s="3"/>
-    </row>
-    <row r="50" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM49" s="3"/>
+      <c r="BN49" s="3"/>
+      <c r="BO49" s="3"/>
+      <c r="BP49" s="3"/>
+    </row>
+    <row r="50" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
       <c r="E50" s="3"/>
@@ -4697,8 +5072,12 @@
       <c r="BJ50" s="3"/>
       <c r="BK50" s="3"/>
       <c r="BL50" s="3"/>
-    </row>
-    <row r="51" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM50" s="3"/>
+      <c r="BN50" s="3"/>
+      <c r="BO50" s="3"/>
+      <c r="BP50" s="3"/>
+    </row>
+    <row r="51" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
       <c r="E51" s="3"/>
@@ -4761,8 +5140,12 @@
       <c r="BJ51" s="3"/>
       <c r="BK51" s="3"/>
       <c r="BL51" s="3"/>
-    </row>
-    <row r="52" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM51" s="3"/>
+      <c r="BN51" s="3"/>
+      <c r="BO51" s="3"/>
+      <c r="BP51" s="3"/>
+    </row>
+    <row r="52" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
@@ -4825,8 +5208,12 @@
       <c r="BJ52" s="3"/>
       <c r="BK52" s="3"/>
       <c r="BL52" s="3"/>
-    </row>
-    <row r="53" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM52" s="3"/>
+      <c r="BN52" s="3"/>
+      <c r="BO52" s="3"/>
+      <c r="BP52" s="3"/>
+    </row>
+    <row r="53" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
@@ -4889,8 +5276,12 @@
       <c r="BJ53" s="3"/>
       <c r="BK53" s="3"/>
       <c r="BL53" s="3"/>
-    </row>
-    <row r="54" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM53" s="3"/>
+      <c r="BN53" s="3"/>
+      <c r="BO53" s="3"/>
+      <c r="BP53" s="3"/>
+    </row>
+    <row r="54" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
@@ -4953,8 +5344,12 @@
       <c r="BJ54" s="3"/>
       <c r="BK54" s="3"/>
       <c r="BL54" s="3"/>
-    </row>
-    <row r="55" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM54" s="3"/>
+      <c r="BN54" s="3"/>
+      <c r="BO54" s="3"/>
+      <c r="BP54" s="3"/>
+    </row>
+    <row r="55" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
@@ -5017,8 +5412,12 @@
       <c r="BJ55" s="3"/>
       <c r="BK55" s="3"/>
       <c r="BL55" s="3"/>
-    </row>
-    <row r="56" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM55" s="3"/>
+      <c r="BN55" s="3"/>
+      <c r="BO55" s="3"/>
+      <c r="BP55" s="3"/>
+    </row>
+    <row r="56" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
@@ -5081,8 +5480,12 @@
       <c r="BJ56" s="3"/>
       <c r="BK56" s="3"/>
       <c r="BL56" s="3"/>
-    </row>
-    <row r="57" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM56" s="3"/>
+      <c r="BN56" s="3"/>
+      <c r="BO56" s="3"/>
+      <c r="BP56" s="3"/>
+    </row>
+    <row r="57" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
@@ -5145,8 +5548,12 @@
       <c r="BJ57" s="3"/>
       <c r="BK57" s="3"/>
       <c r="BL57" s="3"/>
-    </row>
-    <row r="58" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM57" s="3"/>
+      <c r="BN57" s="3"/>
+      <c r="BO57" s="3"/>
+      <c r="BP57" s="3"/>
+    </row>
+    <row r="58" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C58" s="3"/>
       <c r="D58" s="3"/>
       <c r="E58" s="3"/>
@@ -5209,8 +5616,12 @@
       <c r="BJ58" s="3"/>
       <c r="BK58" s="3"/>
       <c r="BL58" s="3"/>
-    </row>
-    <row r="59" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM58" s="3"/>
+      <c r="BN58" s="3"/>
+      <c r="BO58" s="3"/>
+      <c r="BP58" s="3"/>
+    </row>
+    <row r="59" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
@@ -5273,8 +5684,12 @@
       <c r="BJ59" s="3"/>
       <c r="BK59" s="3"/>
       <c r="BL59" s="3"/>
-    </row>
-    <row r="60" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM59" s="3"/>
+      <c r="BN59" s="3"/>
+      <c r="BO59" s="3"/>
+      <c r="BP59" s="3"/>
+    </row>
+    <row r="60" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C60" s="3"/>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
@@ -5337,8 +5752,12 @@
       <c r="BJ60" s="3"/>
       <c r="BK60" s="3"/>
       <c r="BL60" s="3"/>
-    </row>
-    <row r="61" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM60" s="3"/>
+      <c r="BN60" s="3"/>
+      <c r="BO60" s="3"/>
+      <c r="BP60" s="3"/>
+    </row>
+    <row r="61" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
@@ -5401,8 +5820,12 @@
       <c r="BJ61" s="3"/>
       <c r="BK61" s="3"/>
       <c r="BL61" s="3"/>
-    </row>
-    <row r="62" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM61" s="3"/>
+      <c r="BN61" s="3"/>
+      <c r="BO61" s="3"/>
+      <c r="BP61" s="3"/>
+    </row>
+    <row r="62" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
@@ -5465,8 +5888,12 @@
       <c r="BJ62" s="3"/>
       <c r="BK62" s="3"/>
       <c r="BL62" s="3"/>
-    </row>
-    <row r="63" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM62" s="3"/>
+      <c r="BN62" s="3"/>
+      <c r="BO62" s="3"/>
+      <c r="BP62" s="3"/>
+    </row>
+    <row r="63" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
@@ -5529,8 +5956,12 @@
       <c r="BJ63" s="3"/>
       <c r="BK63" s="3"/>
       <c r="BL63" s="3"/>
-    </row>
-    <row r="64" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM63" s="3"/>
+      <c r="BN63" s="3"/>
+      <c r="BO63" s="3"/>
+      <c r="BP63" s="3"/>
+    </row>
+    <row r="64" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
@@ -5593,8 +6024,12 @@
       <c r="BJ64" s="3"/>
       <c r="BK64" s="3"/>
       <c r="BL64" s="3"/>
-    </row>
-    <row r="65" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM64" s="3"/>
+      <c r="BN64" s="3"/>
+      <c r="BO64" s="3"/>
+      <c r="BP64" s="3"/>
+    </row>
+    <row r="65" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C65" s="3"/>
       <c r="D65" s="3"/>
       <c r="E65" s="3"/>
@@ -5657,8 +6092,12 @@
       <c r="BJ65" s="3"/>
       <c r="BK65" s="3"/>
       <c r="BL65" s="3"/>
-    </row>
-    <row r="66" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM65" s="3"/>
+      <c r="BN65" s="3"/>
+      <c r="BO65" s="3"/>
+      <c r="BP65" s="3"/>
+    </row>
+    <row r="66" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C66" s="3"/>
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
@@ -5721,8 +6160,12 @@
       <c r="BJ66" s="3"/>
       <c r="BK66" s="3"/>
       <c r="BL66" s="3"/>
-    </row>
-    <row r="67" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM66" s="3"/>
+      <c r="BN66" s="3"/>
+      <c r="BO66" s="3"/>
+      <c r="BP66" s="3"/>
+    </row>
+    <row r="67" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C67" s="3"/>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
@@ -5785,8 +6228,12 @@
       <c r="BJ67" s="3"/>
       <c r="BK67" s="3"/>
       <c r="BL67" s="3"/>
-    </row>
-    <row r="68" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM67" s="3"/>
+      <c r="BN67" s="3"/>
+      <c r="BO67" s="3"/>
+      <c r="BP67" s="3"/>
+    </row>
+    <row r="68" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
@@ -5849,8 +6296,12 @@
       <c r="BJ68" s="3"/>
       <c r="BK68" s="3"/>
       <c r="BL68" s="3"/>
-    </row>
-    <row r="69" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM68" s="3"/>
+      <c r="BN68" s="3"/>
+      <c r="BO68" s="3"/>
+      <c r="BP68" s="3"/>
+    </row>
+    <row r="69" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C69" s="3"/>
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
@@ -5913,8 +6364,12 @@
       <c r="BJ69" s="3"/>
       <c r="BK69" s="3"/>
       <c r="BL69" s="3"/>
-    </row>
-    <row r="70" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM69" s="3"/>
+      <c r="BN69" s="3"/>
+      <c r="BO69" s="3"/>
+      <c r="BP69" s="3"/>
+    </row>
+    <row r="70" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C70" s="3"/>
       <c r="D70" s="3"/>
       <c r="E70" s="3"/>
@@ -5977,8 +6432,12 @@
       <c r="BJ70" s="3"/>
       <c r="BK70" s="3"/>
       <c r="BL70" s="3"/>
-    </row>
-    <row r="71" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM70" s="3"/>
+      <c r="BN70" s="3"/>
+      <c r="BO70" s="3"/>
+      <c r="BP70" s="3"/>
+    </row>
+    <row r="71" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C71" s="3"/>
       <c r="D71" s="3"/>
       <c r="E71" s="3"/>
@@ -6041,8 +6500,12 @@
       <c r="BJ71" s="3"/>
       <c r="BK71" s="3"/>
       <c r="BL71" s="3"/>
-    </row>
-    <row r="72" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM71" s="3"/>
+      <c r="BN71" s="3"/>
+      <c r="BO71" s="3"/>
+      <c r="BP71" s="3"/>
+    </row>
+    <row r="72" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C72" s="3"/>
       <c r="D72" s="3"/>
       <c r="E72" s="3"/>
@@ -6105,8 +6568,12 @@
       <c r="BJ72" s="3"/>
       <c r="BK72" s="3"/>
       <c r="BL72" s="3"/>
-    </row>
-    <row r="73" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM72" s="3"/>
+      <c r="BN72" s="3"/>
+      <c r="BO72" s="3"/>
+      <c r="BP72" s="3"/>
+    </row>
+    <row r="73" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C73" s="3"/>
       <c r="D73" s="3"/>
       <c r="E73" s="3"/>
@@ -6169,8 +6636,12 @@
       <c r="BJ73" s="3"/>
       <c r="BK73" s="3"/>
       <c r="BL73" s="3"/>
-    </row>
-    <row r="74" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM73" s="3"/>
+      <c r="BN73" s="3"/>
+      <c r="BO73" s="3"/>
+      <c r="BP73" s="3"/>
+    </row>
+    <row r="74" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C74" s="3"/>
       <c r="D74" s="3"/>
       <c r="E74" s="3"/>
@@ -6233,8 +6704,12 @@
       <c r="BJ74" s="3"/>
       <c r="BK74" s="3"/>
       <c r="BL74" s="3"/>
-    </row>
-    <row r="75" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM74" s="3"/>
+      <c r="BN74" s="3"/>
+      <c r="BO74" s="3"/>
+      <c r="BP74" s="3"/>
+    </row>
+    <row r="75" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C75" s="3"/>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
@@ -6297,8 +6772,12 @@
       <c r="BJ75" s="3"/>
       <c r="BK75" s="3"/>
       <c r="BL75" s="3"/>
-    </row>
-    <row r="76" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM75" s="3"/>
+      <c r="BN75" s="3"/>
+      <c r="BO75" s="3"/>
+      <c r="BP75" s="3"/>
+    </row>
+    <row r="76" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
@@ -6361,8 +6840,12 @@
       <c r="BJ76" s="3"/>
       <c r="BK76" s="3"/>
       <c r="BL76" s="3"/>
-    </row>
-    <row r="77" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM76" s="3"/>
+      <c r="BN76" s="3"/>
+      <c r="BO76" s="3"/>
+      <c r="BP76" s="3"/>
+    </row>
+    <row r="77" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
@@ -6425,8 +6908,12 @@
       <c r="BJ77" s="3"/>
       <c r="BK77" s="3"/>
       <c r="BL77" s="3"/>
-    </row>
-    <row r="78" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM77" s="3"/>
+      <c r="BN77" s="3"/>
+      <c r="BO77" s="3"/>
+      <c r="BP77" s="3"/>
+    </row>
+    <row r="78" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
@@ -6489,8 +6976,12 @@
       <c r="BJ78" s="3"/>
       <c r="BK78" s="3"/>
       <c r="BL78" s="3"/>
-    </row>
-    <row r="79" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM78" s="3"/>
+      <c r="BN78" s="3"/>
+      <c r="BO78" s="3"/>
+      <c r="BP78" s="3"/>
+    </row>
+    <row r="79" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
@@ -6553,8 +7044,12 @@
       <c r="BJ79" s="3"/>
       <c r="BK79" s="3"/>
       <c r="BL79" s="3"/>
-    </row>
-    <row r="80" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM79" s="3"/>
+      <c r="BN79" s="3"/>
+      <c r="BO79" s="3"/>
+      <c r="BP79" s="3"/>
+    </row>
+    <row r="80" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
@@ -6617,8 +7112,12 @@
       <c r="BJ80" s="3"/>
       <c r="BK80" s="3"/>
       <c r="BL80" s="3"/>
-    </row>
-    <row r="81" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM80" s="3"/>
+      <c r="BN80" s="3"/>
+      <c r="BO80" s="3"/>
+      <c r="BP80" s="3"/>
+    </row>
+    <row r="81" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
@@ -6681,8 +7180,12 @@
       <c r="BJ81" s="3"/>
       <c r="BK81" s="3"/>
       <c r="BL81" s="3"/>
-    </row>
-    <row r="82" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM81" s="3"/>
+      <c r="BN81" s="3"/>
+      <c r="BO81" s="3"/>
+      <c r="BP81" s="3"/>
+    </row>
+    <row r="82" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
@@ -6745,8 +7248,12 @@
       <c r="BJ82" s="3"/>
       <c r="BK82" s="3"/>
       <c r="BL82" s="3"/>
-    </row>
-    <row r="83" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM82" s="3"/>
+      <c r="BN82" s="3"/>
+      <c r="BO82" s="3"/>
+      <c r="BP82" s="3"/>
+    </row>
+    <row r="83" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
@@ -6809,8 +7316,12 @@
       <c r="BJ83" s="3"/>
       <c r="BK83" s="3"/>
       <c r="BL83" s="3"/>
-    </row>
-    <row r="84" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM83" s="3"/>
+      <c r="BN83" s="3"/>
+      <c r="BO83" s="3"/>
+      <c r="BP83" s="3"/>
+    </row>
+    <row r="84" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
@@ -6873,8 +7384,12 @@
       <c r="BJ84" s="3"/>
       <c r="BK84" s="3"/>
       <c r="BL84" s="3"/>
-    </row>
-    <row r="85" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM84" s="3"/>
+      <c r="BN84" s="3"/>
+      <c r="BO84" s="3"/>
+      <c r="BP84" s="3"/>
+    </row>
+    <row r="85" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
@@ -6937,8 +7452,12 @@
       <c r="BJ85" s="3"/>
       <c r="BK85" s="3"/>
       <c r="BL85" s="3"/>
-    </row>
-    <row r="86" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM85" s="3"/>
+      <c r="BN85" s="3"/>
+      <c r="BO85" s="3"/>
+      <c r="BP85" s="3"/>
+    </row>
+    <row r="86" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
@@ -7001,8 +7520,12 @@
       <c r="BJ86" s="3"/>
       <c r="BK86" s="3"/>
       <c r="BL86" s="3"/>
-    </row>
-    <row r="87" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM86" s="3"/>
+      <c r="BN86" s="3"/>
+      <c r="BO86" s="3"/>
+      <c r="BP86" s="3"/>
+    </row>
+    <row r="87" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
@@ -7065,8 +7588,12 @@
       <c r="BJ87" s="3"/>
       <c r="BK87" s="3"/>
       <c r="BL87" s="3"/>
-    </row>
-    <row r="88" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM87" s="3"/>
+      <c r="BN87" s="3"/>
+      <c r="BO87" s="3"/>
+      <c r="BP87" s="3"/>
+    </row>
+    <row r="88" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
@@ -7129,8 +7656,12 @@
       <c r="BJ88" s="3"/>
       <c r="BK88" s="3"/>
       <c r="BL88" s="3"/>
-    </row>
-    <row r="89" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM88" s="3"/>
+      <c r="BN88" s="3"/>
+      <c r="BO88" s="3"/>
+      <c r="BP88" s="3"/>
+    </row>
+    <row r="89" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C89" s="3"/>
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
@@ -7193,8 +7724,12 @@
       <c r="BJ89" s="3"/>
       <c r="BK89" s="3"/>
       <c r="BL89" s="3"/>
-    </row>
-    <row r="90" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM89" s="3"/>
+      <c r="BN89" s="3"/>
+      <c r="BO89" s="3"/>
+      <c r="BP89" s="3"/>
+    </row>
+    <row r="90" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
       <c r="E90" s="3"/>
@@ -7257,8 +7792,12 @@
       <c r="BJ90" s="3"/>
       <c r="BK90" s="3"/>
       <c r="BL90" s="3"/>
-    </row>
-    <row r="91" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM90" s="3"/>
+      <c r="BN90" s="3"/>
+      <c r="BO90" s="3"/>
+      <c r="BP90" s="3"/>
+    </row>
+    <row r="91" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
@@ -7321,8 +7860,12 @@
       <c r="BJ91" s="3"/>
       <c r="BK91" s="3"/>
       <c r="BL91" s="3"/>
-    </row>
-    <row r="92" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM91" s="3"/>
+      <c r="BN91" s="3"/>
+      <c r="BO91" s="3"/>
+      <c r="BP91" s="3"/>
+    </row>
+    <row r="92" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
@@ -7385,8 +7928,12 @@
       <c r="BJ92" s="3"/>
       <c r="BK92" s="3"/>
       <c r="BL92" s="3"/>
-    </row>
-    <row r="93" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM92" s="3"/>
+      <c r="BN92" s="3"/>
+      <c r="BO92" s="3"/>
+      <c r="BP92" s="3"/>
+    </row>
+    <row r="93" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
@@ -7449,8 +7996,12 @@
       <c r="BJ93" s="3"/>
       <c r="BK93" s="3"/>
       <c r="BL93" s="3"/>
-    </row>
-    <row r="94" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM93" s="3"/>
+      <c r="BN93" s="3"/>
+      <c r="BO93" s="3"/>
+      <c r="BP93" s="3"/>
+    </row>
+    <row r="94" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
@@ -7513,8 +8064,12 @@
       <c r="BJ94" s="3"/>
       <c r="BK94" s="3"/>
       <c r="BL94" s="3"/>
-    </row>
-    <row r="95" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM94" s="3"/>
+      <c r="BN94" s="3"/>
+      <c r="BO94" s="3"/>
+      <c r="BP94" s="3"/>
+    </row>
+    <row r="95" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
@@ -7577,8 +8132,12 @@
       <c r="BJ95" s="3"/>
       <c r="BK95" s="3"/>
       <c r="BL95" s="3"/>
-    </row>
-    <row r="96" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM95" s="3"/>
+      <c r="BN95" s="3"/>
+      <c r="BO95" s="3"/>
+      <c r="BP95" s="3"/>
+    </row>
+    <row r="96" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
@@ -7641,8 +8200,12 @@
       <c r="BJ96" s="3"/>
       <c r="BK96" s="3"/>
       <c r="BL96" s="3"/>
-    </row>
-    <row r="97" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM96" s="3"/>
+      <c r="BN96" s="3"/>
+      <c r="BO96" s="3"/>
+      <c r="BP96" s="3"/>
+    </row>
+    <row r="97" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
@@ -7705,8 +8268,12 @@
       <c r="BJ97" s="3"/>
       <c r="BK97" s="3"/>
       <c r="BL97" s="3"/>
-    </row>
-    <row r="98" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM97" s="3"/>
+      <c r="BN97" s="3"/>
+      <c r="BO97" s="3"/>
+      <c r="BP97" s="3"/>
+    </row>
+    <row r="98" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
@@ -7769,8 +8336,12 @@
       <c r="BJ98" s="3"/>
       <c r="BK98" s="3"/>
       <c r="BL98" s="3"/>
-    </row>
-    <row r="99" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM98" s="3"/>
+      <c r="BN98" s="3"/>
+      <c r="BO98" s="3"/>
+      <c r="BP98" s="3"/>
+    </row>
+    <row r="99" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
@@ -7833,8 +8404,12 @@
       <c r="BJ99" s="3"/>
       <c r="BK99" s="3"/>
       <c r="BL99" s="3"/>
-    </row>
-    <row r="100" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM99" s="3"/>
+      <c r="BN99" s="3"/>
+      <c r="BO99" s="3"/>
+      <c r="BP99" s="3"/>
+    </row>
+    <row r="100" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
@@ -7897,8 +8472,12 @@
       <c r="BJ100" s="3"/>
       <c r="BK100" s="3"/>
       <c r="BL100" s="3"/>
-    </row>
-    <row r="101" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM100" s="3"/>
+      <c r="BN100" s="3"/>
+      <c r="BO100" s="3"/>
+      <c r="BP100" s="3"/>
+    </row>
+    <row r="101" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C101" s="3"/>
       <c r="D101" s="3"/>
       <c r="E101" s="3"/>
@@ -7961,8 +8540,12 @@
       <c r="BJ101" s="3"/>
       <c r="BK101" s="3"/>
       <c r="BL101" s="3"/>
-    </row>
-    <row r="102" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM101" s="3"/>
+      <c r="BN101" s="3"/>
+      <c r="BO101" s="3"/>
+      <c r="BP101" s="3"/>
+    </row>
+    <row r="102" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C102" s="3"/>
       <c r="D102" s="3"/>
       <c r="E102" s="3"/>
@@ -8025,8 +8608,12 @@
       <c r="BJ102" s="3"/>
       <c r="BK102" s="3"/>
       <c r="BL102" s="3"/>
-    </row>
-    <row r="103" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM102" s="3"/>
+      <c r="BN102" s="3"/>
+      <c r="BO102" s="3"/>
+      <c r="BP102" s="3"/>
+    </row>
+    <row r="103" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C103" s="3"/>
       <c r="D103" s="3"/>
       <c r="E103" s="3"/>
@@ -8089,8 +8676,12 @@
       <c r="BJ103" s="3"/>
       <c r="BK103" s="3"/>
       <c r="BL103" s="3"/>
-    </row>
-    <row r="104" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM103" s="3"/>
+      <c r="BN103" s="3"/>
+      <c r="BO103" s="3"/>
+      <c r="BP103" s="3"/>
+    </row>
+    <row r="104" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C104" s="3"/>
       <c r="D104" s="3"/>
       <c r="E104" s="3"/>
@@ -8153,8 +8744,12 @@
       <c r="BJ104" s="3"/>
       <c r="BK104" s="3"/>
       <c r="BL104" s="3"/>
-    </row>
-    <row r="105" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM104" s="3"/>
+      <c r="BN104" s="3"/>
+      <c r="BO104" s="3"/>
+      <c r="BP104" s="3"/>
+    </row>
+    <row r="105" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C105" s="3"/>
       <c r="D105" s="3"/>
       <c r="E105" s="3"/>
@@ -8217,8 +8812,12 @@
       <c r="BJ105" s="3"/>
       <c r="BK105" s="3"/>
       <c r="BL105" s="3"/>
-    </row>
-    <row r="106" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM105" s="3"/>
+      <c r="BN105" s="3"/>
+      <c r="BO105" s="3"/>
+      <c r="BP105" s="3"/>
+    </row>
+    <row r="106" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C106" s="3"/>
       <c r="D106" s="3"/>
       <c r="E106" s="3"/>
@@ -8281,8 +8880,12 @@
       <c r="BJ106" s="3"/>
       <c r="BK106" s="3"/>
       <c r="BL106" s="3"/>
-    </row>
-    <row r="107" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM106" s="3"/>
+      <c r="BN106" s="3"/>
+      <c r="BO106" s="3"/>
+      <c r="BP106" s="3"/>
+    </row>
+    <row r="107" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C107" s="3"/>
       <c r="D107" s="3"/>
       <c r="E107" s="3"/>
@@ -8345,8 +8948,12 @@
       <c r="BJ107" s="3"/>
       <c r="BK107" s="3"/>
       <c r="BL107" s="3"/>
-    </row>
-    <row r="108" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM107" s="3"/>
+      <c r="BN107" s="3"/>
+      <c r="BO107" s="3"/>
+      <c r="BP107" s="3"/>
+    </row>
+    <row r="108" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C108" s="3"/>
       <c r="D108" s="3"/>
       <c r="E108" s="3"/>
@@ -8409,8 +9016,12 @@
       <c r="BJ108" s="3"/>
       <c r="BK108" s="3"/>
       <c r="BL108" s="3"/>
-    </row>
-    <row r="109" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM108" s="3"/>
+      <c r="BN108" s="3"/>
+      <c r="BO108" s="3"/>
+      <c r="BP108" s="3"/>
+    </row>
+    <row r="109" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C109" s="3"/>
       <c r="D109" s="3"/>
       <c r="E109" s="3"/>
@@ -8473,8 +9084,12 @@
       <c r="BJ109" s="3"/>
       <c r="BK109" s="3"/>
       <c r="BL109" s="3"/>
-    </row>
-    <row r="110" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM109" s="3"/>
+      <c r="BN109" s="3"/>
+      <c r="BO109" s="3"/>
+      <c r="BP109" s="3"/>
+    </row>
+    <row r="110" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C110" s="3"/>
       <c r="D110" s="3"/>
       <c r="E110" s="3"/>
@@ -8537,8 +9152,12 @@
       <c r="BJ110" s="3"/>
       <c r="BK110" s="3"/>
       <c r="BL110" s="3"/>
-    </row>
-    <row r="111" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM110" s="3"/>
+      <c r="BN110" s="3"/>
+      <c r="BO110" s="3"/>
+      <c r="BP110" s="3"/>
+    </row>
+    <row r="111" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C111" s="3"/>
       <c r="D111" s="3"/>
       <c r="E111" s="3"/>
@@ -8601,8 +9220,12 @@
       <c r="BJ111" s="3"/>
       <c r="BK111" s="3"/>
       <c r="BL111" s="3"/>
-    </row>
-    <row r="112" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM111" s="3"/>
+      <c r="BN111" s="3"/>
+      <c r="BO111" s="3"/>
+      <c r="BP111" s="3"/>
+    </row>
+    <row r="112" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C112" s="3"/>
       <c r="D112" s="3"/>
       <c r="E112" s="3"/>
@@ -8665,8 +9288,12 @@
       <c r="BJ112" s="3"/>
       <c r="BK112" s="3"/>
       <c r="BL112" s="3"/>
-    </row>
-    <row r="113" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM112" s="3"/>
+      <c r="BN112" s="3"/>
+      <c r="BO112" s="3"/>
+      <c r="BP112" s="3"/>
+    </row>
+    <row r="113" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C113" s="3"/>
       <c r="D113" s="3"/>
       <c r="E113" s="3"/>
@@ -8729,8 +9356,12 @@
       <c r="BJ113" s="3"/>
       <c r="BK113" s="3"/>
       <c r="BL113" s="3"/>
-    </row>
-    <row r="114" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM113" s="3"/>
+      <c r="BN113" s="3"/>
+      <c r="BO113" s="3"/>
+      <c r="BP113" s="3"/>
+    </row>
+    <row r="114" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C114" s="3"/>
       <c r="D114" s="3"/>
       <c r="E114" s="3"/>
@@ -8793,8 +9424,12 @@
       <c r="BJ114" s="3"/>
       <c r="BK114" s="3"/>
       <c r="BL114" s="3"/>
-    </row>
-    <row r="115" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM114" s="3"/>
+      <c r="BN114" s="3"/>
+      <c r="BO114" s="3"/>
+      <c r="BP114" s="3"/>
+    </row>
+    <row r="115" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C115" s="3"/>
       <c r="D115" s="3"/>
       <c r="E115" s="3"/>
@@ -8857,8 +9492,12 @@
       <c r="BJ115" s="3"/>
       <c r="BK115" s="3"/>
       <c r="BL115" s="3"/>
-    </row>
-    <row r="116" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM115" s="3"/>
+      <c r="BN115" s="3"/>
+      <c r="BO115" s="3"/>
+      <c r="BP115" s="3"/>
+    </row>
+    <row r="116" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C116" s="3"/>
       <c r="D116" s="3"/>
       <c r="E116" s="3"/>
@@ -8921,8 +9560,12 @@
       <c r="BJ116" s="3"/>
       <c r="BK116" s="3"/>
       <c r="BL116" s="3"/>
-    </row>
-    <row r="117" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM116" s="3"/>
+      <c r="BN116" s="3"/>
+      <c r="BO116" s="3"/>
+      <c r="BP116" s="3"/>
+    </row>
+    <row r="117" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C117" s="3"/>
       <c r="D117" s="3"/>
       <c r="E117" s="3"/>
@@ -8985,8 +9628,12 @@
       <c r="BJ117" s="3"/>
       <c r="BK117" s="3"/>
       <c r="BL117" s="3"/>
-    </row>
-    <row r="118" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM117" s="3"/>
+      <c r="BN117" s="3"/>
+      <c r="BO117" s="3"/>
+      <c r="BP117" s="3"/>
+    </row>
+    <row r="118" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C118" s="3"/>
       <c r="D118" s="3"/>
       <c r="E118" s="3"/>
@@ -9049,8 +9696,12 @@
       <c r="BJ118" s="3"/>
       <c r="BK118" s="3"/>
       <c r="BL118" s="3"/>
-    </row>
-    <row r="119" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM118" s="3"/>
+      <c r="BN118" s="3"/>
+      <c r="BO118" s="3"/>
+      <c r="BP118" s="3"/>
+    </row>
+    <row r="119" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C119" s="3"/>
       <c r="D119" s="3"/>
       <c r="E119" s="3"/>
@@ -9113,8 +9764,12 @@
       <c r="BJ119" s="3"/>
       <c r="BK119" s="3"/>
       <c r="BL119" s="3"/>
-    </row>
-    <row r="120" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM119" s="3"/>
+      <c r="BN119" s="3"/>
+      <c r="BO119" s="3"/>
+      <c r="BP119" s="3"/>
+    </row>
+    <row r="120" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C120" s="3"/>
       <c r="D120" s="3"/>
       <c r="E120" s="3"/>
@@ -9177,8 +9832,12 @@
       <c r="BJ120" s="3"/>
       <c r="BK120" s="3"/>
       <c r="BL120" s="3"/>
-    </row>
-    <row r="121" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM120" s="3"/>
+      <c r="BN120" s="3"/>
+      <c r="BO120" s="3"/>
+      <c r="BP120" s="3"/>
+    </row>
+    <row r="121" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C121" s="3"/>
       <c r="D121" s="3"/>
       <c r="E121" s="3"/>
@@ -9241,8 +9900,12 @@
       <c r="BJ121" s="3"/>
       <c r="BK121" s="3"/>
       <c r="BL121" s="3"/>
-    </row>
-    <row r="122" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM121" s="3"/>
+      <c r="BN121" s="3"/>
+      <c r="BO121" s="3"/>
+      <c r="BP121" s="3"/>
+    </row>
+    <row r="122" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C122" s="3"/>
       <c r="D122" s="3"/>
       <c r="E122" s="3"/>
@@ -9305,8 +9968,12 @@
       <c r="BJ122" s="3"/>
       <c r="BK122" s="3"/>
       <c r="BL122" s="3"/>
-    </row>
-    <row r="123" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM122" s="3"/>
+      <c r="BN122" s="3"/>
+      <c r="BO122" s="3"/>
+      <c r="BP122" s="3"/>
+    </row>
+    <row r="123" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C123" s="3"/>
       <c r="D123" s="3"/>
       <c r="E123" s="3"/>
@@ -9369,8 +10036,12 @@
       <c r="BJ123" s="3"/>
       <c r="BK123" s="3"/>
       <c r="BL123" s="3"/>
-    </row>
-    <row r="124" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM123" s="3"/>
+      <c r="BN123" s="3"/>
+      <c r="BO123" s="3"/>
+      <c r="BP123" s="3"/>
+    </row>
+    <row r="124" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C124" s="3"/>
       <c r="D124" s="3"/>
       <c r="E124" s="3"/>
@@ -9433,8 +10104,12 @@
       <c r="BJ124" s="3"/>
       <c r="BK124" s="3"/>
       <c r="BL124" s="3"/>
-    </row>
-    <row r="125" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM124" s="3"/>
+      <c r="BN124" s="3"/>
+      <c r="BO124" s="3"/>
+      <c r="BP124" s="3"/>
+    </row>
+    <row r="125" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C125" s="3"/>
       <c r="D125" s="3"/>
       <c r="E125" s="3"/>
@@ -9497,8 +10172,12 @@
       <c r="BJ125" s="3"/>
       <c r="BK125" s="3"/>
       <c r="BL125" s="3"/>
-    </row>
-    <row r="126" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM125" s="3"/>
+      <c r="BN125" s="3"/>
+      <c r="BO125" s="3"/>
+      <c r="BP125" s="3"/>
+    </row>
+    <row r="126" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C126" s="3"/>
       <c r="D126" s="3"/>
       <c r="E126" s="3"/>
@@ -9561,8 +10240,12 @@
       <c r="BJ126" s="3"/>
       <c r="BK126" s="3"/>
       <c r="BL126" s="3"/>
-    </row>
-    <row r="127" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM126" s="3"/>
+      <c r="BN126" s="3"/>
+      <c r="BO126" s="3"/>
+      <c r="BP126" s="3"/>
+    </row>
+    <row r="127" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C127" s="3"/>
       <c r="D127" s="3"/>
       <c r="E127" s="3"/>
@@ -9625,8 +10308,12 @@
       <c r="BJ127" s="3"/>
       <c r="BK127" s="3"/>
       <c r="BL127" s="3"/>
-    </row>
-    <row r="128" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM127" s="3"/>
+      <c r="BN127" s="3"/>
+      <c r="BO127" s="3"/>
+      <c r="BP127" s="3"/>
+    </row>
+    <row r="128" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C128" s="3"/>
       <c r="D128" s="3"/>
       <c r="E128" s="3"/>
@@ -9689,8 +10376,12 @@
       <c r="BJ128" s="3"/>
       <c r="BK128" s="3"/>
       <c r="BL128" s="3"/>
-    </row>
-    <row r="129" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM128" s="3"/>
+      <c r="BN128" s="3"/>
+      <c r="BO128" s="3"/>
+      <c r="BP128" s="3"/>
+    </row>
+    <row r="129" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C129" s="3"/>
       <c r="D129" s="3"/>
       <c r="E129" s="3"/>
@@ -9753,8 +10444,12 @@
       <c r="BJ129" s="3"/>
       <c r="BK129" s="3"/>
       <c r="BL129" s="3"/>
-    </row>
-    <row r="130" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM129" s="3"/>
+      <c r="BN129" s="3"/>
+      <c r="BO129" s="3"/>
+      <c r="BP129" s="3"/>
+    </row>
+    <row r="130" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C130" s="3"/>
       <c r="D130" s="3"/>
       <c r="E130" s="3"/>
@@ -9817,8 +10512,12 @@
       <c r="BJ130" s="3"/>
       <c r="BK130" s="3"/>
       <c r="BL130" s="3"/>
-    </row>
-    <row r="131" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM130" s="3"/>
+      <c r="BN130" s="3"/>
+      <c r="BO130" s="3"/>
+      <c r="BP130" s="3"/>
+    </row>
+    <row r="131" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C131" s="3"/>
       <c r="D131" s="3"/>
       <c r="E131" s="3"/>
@@ -9881,8 +10580,12 @@
       <c r="BJ131" s="3"/>
       <c r="BK131" s="3"/>
       <c r="BL131" s="3"/>
-    </row>
-    <row r="132" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM131" s="3"/>
+      <c r="BN131" s="3"/>
+      <c r="BO131" s="3"/>
+      <c r="BP131" s="3"/>
+    </row>
+    <row r="132" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C132" s="3"/>
       <c r="D132" s="3"/>
       <c r="E132" s="3"/>
@@ -9945,8 +10648,12 @@
       <c r="BJ132" s="3"/>
       <c r="BK132" s="3"/>
       <c r="BL132" s="3"/>
-    </row>
-    <row r="133" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM132" s="3"/>
+      <c r="BN132" s="3"/>
+      <c r="BO132" s="3"/>
+      <c r="BP132" s="3"/>
+    </row>
+    <row r="133" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C133" s="3"/>
       <c r="D133" s="3"/>
       <c r="E133" s="3"/>
@@ -10009,8 +10716,12 @@
       <c r="BJ133" s="3"/>
       <c r="BK133" s="3"/>
       <c r="BL133" s="3"/>
-    </row>
-    <row r="134" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM133" s="3"/>
+      <c r="BN133" s="3"/>
+      <c r="BO133" s="3"/>
+      <c r="BP133" s="3"/>
+    </row>
+    <row r="134" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C134" s="3"/>
       <c r="D134" s="3"/>
       <c r="E134" s="3"/>
@@ -10073,8 +10784,12 @@
       <c r="BJ134" s="3"/>
       <c r="BK134" s="3"/>
       <c r="BL134" s="3"/>
-    </row>
-    <row r="135" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM134" s="3"/>
+      <c r="BN134" s="3"/>
+      <c r="BO134" s="3"/>
+      <c r="BP134" s="3"/>
+    </row>
+    <row r="135" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C135" s="3"/>
       <c r="D135" s="3"/>
       <c r="E135" s="3"/>
@@ -10137,8 +10852,12 @@
       <c r="BJ135" s="3"/>
       <c r="BK135" s="3"/>
       <c r="BL135" s="3"/>
-    </row>
-    <row r="136" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM135" s="3"/>
+      <c r="BN135" s="3"/>
+      <c r="BO135" s="3"/>
+      <c r="BP135" s="3"/>
+    </row>
+    <row r="136" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C136" s="3"/>
       <c r="D136" s="3"/>
       <c r="E136" s="3"/>
@@ -10201,8 +10920,12 @@
       <c r="BJ136" s="3"/>
       <c r="BK136" s="3"/>
       <c r="BL136" s="3"/>
-    </row>
-    <row r="137" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM136" s="3"/>
+      <c r="BN136" s="3"/>
+      <c r="BO136" s="3"/>
+      <c r="BP136" s="3"/>
+    </row>
+    <row r="137" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C137" s="3"/>
       <c r="D137" s="3"/>
       <c r="E137" s="3"/>
@@ -10265,8 +10988,12 @@
       <c r="BJ137" s="3"/>
       <c r="BK137" s="3"/>
       <c r="BL137" s="3"/>
-    </row>
-    <row r="138" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM137" s="3"/>
+      <c r="BN137" s="3"/>
+      <c r="BO137" s="3"/>
+      <c r="BP137" s="3"/>
+    </row>
+    <row r="138" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C138" s="3"/>
       <c r="D138" s="3"/>
       <c r="E138" s="3"/>
@@ -10329,8 +11056,12 @@
       <c r="BJ138" s="3"/>
       <c r="BK138" s="3"/>
       <c r="BL138" s="3"/>
-    </row>
-    <row r="139" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM138" s="3"/>
+      <c r="BN138" s="3"/>
+      <c r="BO138" s="3"/>
+      <c r="BP138" s="3"/>
+    </row>
+    <row r="139" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C139" s="3"/>
       <c r="D139" s="3"/>
       <c r="E139" s="3"/>
@@ -10393,8 +11124,12 @@
       <c r="BJ139" s="3"/>
       <c r="BK139" s="3"/>
       <c r="BL139" s="3"/>
-    </row>
-    <row r="140" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM139" s="3"/>
+      <c r="BN139" s="3"/>
+      <c r="BO139" s="3"/>
+      <c r="BP139" s="3"/>
+    </row>
+    <row r="140" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C140" s="3"/>
       <c r="D140" s="3"/>
       <c r="E140" s="3"/>
@@ -10457,8 +11192,12 @@
       <c r="BJ140" s="3"/>
       <c r="BK140" s="3"/>
       <c r="BL140" s="3"/>
-    </row>
-    <row r="141" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM140" s="3"/>
+      <c r="BN140" s="3"/>
+      <c r="BO140" s="3"/>
+      <c r="BP140" s="3"/>
+    </row>
+    <row r="141" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C141" s="3"/>
       <c r="D141" s="3"/>
       <c r="E141" s="3"/>
@@ -10521,8 +11260,12 @@
       <c r="BJ141" s="3"/>
       <c r="BK141" s="3"/>
       <c r="BL141" s="3"/>
-    </row>
-    <row r="142" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM141" s="3"/>
+      <c r="BN141" s="3"/>
+      <c r="BO141" s="3"/>
+      <c r="BP141" s="3"/>
+    </row>
+    <row r="142" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C142" s="3"/>
       <c r="D142" s="3"/>
       <c r="E142" s="3"/>
@@ -10585,8 +11328,12 @@
       <c r="BJ142" s="3"/>
       <c r="BK142" s="3"/>
       <c r="BL142" s="3"/>
-    </row>
-    <row r="143" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM142" s="3"/>
+      <c r="BN142" s="3"/>
+      <c r="BO142" s="3"/>
+      <c r="BP142" s="3"/>
+    </row>
+    <row r="143" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C143" s="3"/>
       <c r="D143" s="3"/>
       <c r="E143" s="3"/>
@@ -10649,8 +11396,12 @@
       <c r="BJ143" s="3"/>
       <c r="BK143" s="3"/>
       <c r="BL143" s="3"/>
-    </row>
-    <row r="144" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM143" s="3"/>
+      <c r="BN143" s="3"/>
+      <c r="BO143" s="3"/>
+      <c r="BP143" s="3"/>
+    </row>
+    <row r="144" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C144" s="3"/>
       <c r="D144" s="3"/>
       <c r="E144" s="3"/>
@@ -10713,8 +11464,12 @@
       <c r="BJ144" s="3"/>
       <c r="BK144" s="3"/>
       <c r="BL144" s="3"/>
-    </row>
-    <row r="145" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM144" s="3"/>
+      <c r="BN144" s="3"/>
+      <c r="BO144" s="3"/>
+      <c r="BP144" s="3"/>
+    </row>
+    <row r="145" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C145" s="3"/>
       <c r="D145" s="3"/>
       <c r="E145" s="3"/>
@@ -10777,8 +11532,12 @@
       <c r="BJ145" s="3"/>
       <c r="BK145" s="3"/>
       <c r="BL145" s="3"/>
-    </row>
-    <row r="146" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM145" s="3"/>
+      <c r="BN145" s="3"/>
+      <c r="BO145" s="3"/>
+      <c r="BP145" s="3"/>
+    </row>
+    <row r="146" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C146" s="3"/>
       <c r="D146" s="3"/>
       <c r="E146" s="3"/>
@@ -10841,8 +11600,12 @@
       <c r="BJ146" s="3"/>
       <c r="BK146" s="3"/>
       <c r="BL146" s="3"/>
-    </row>
-    <row r="147" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM146" s="3"/>
+      <c r="BN146" s="3"/>
+      <c r="BO146" s="3"/>
+      <c r="BP146" s="3"/>
+    </row>
+    <row r="147" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C147" s="3"/>
       <c r="D147" s="3"/>
       <c r="E147" s="3"/>
@@ -10905,8 +11668,12 @@
       <c r="BJ147" s="3"/>
       <c r="BK147" s="3"/>
       <c r="BL147" s="3"/>
-    </row>
-    <row r="148" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM147" s="3"/>
+      <c r="BN147" s="3"/>
+      <c r="BO147" s="3"/>
+      <c r="BP147" s="3"/>
+    </row>
+    <row r="148" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C148" s="3"/>
       <c r="D148" s="3"/>
       <c r="E148" s="3"/>
@@ -10969,8 +11736,12 @@
       <c r="BJ148" s="3"/>
       <c r="BK148" s="3"/>
       <c r="BL148" s="3"/>
-    </row>
-    <row r="149" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM148" s="3"/>
+      <c r="BN148" s="3"/>
+      <c r="BO148" s="3"/>
+      <c r="BP148" s="3"/>
+    </row>
+    <row r="149" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C149" s="3"/>
       <c r="D149" s="3"/>
       <c r="E149" s="3"/>
@@ -11033,8 +11804,12 @@
       <c r="BJ149" s="3"/>
       <c r="BK149" s="3"/>
       <c r="BL149" s="3"/>
-    </row>
-    <row r="150" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM149" s="3"/>
+      <c r="BN149" s="3"/>
+      <c r="BO149" s="3"/>
+      <c r="BP149" s="3"/>
+    </row>
+    <row r="150" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C150" s="3"/>
       <c r="D150" s="3"/>
       <c r="E150" s="3"/>
@@ -11097,8 +11872,12 @@
       <c r="BJ150" s="3"/>
       <c r="BK150" s="3"/>
       <c r="BL150" s="3"/>
-    </row>
-    <row r="151" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM150" s="3"/>
+      <c r="BN150" s="3"/>
+      <c r="BO150" s="3"/>
+      <c r="BP150" s="3"/>
+    </row>
+    <row r="151" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C151" s="3"/>
       <c r="D151" s="3"/>
       <c r="E151" s="3"/>
@@ -11161,8 +11940,12 @@
       <c r="BJ151" s="3"/>
       <c r="BK151" s="3"/>
       <c r="BL151" s="3"/>
-    </row>
-    <row r="152" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM151" s="3"/>
+      <c r="BN151" s="3"/>
+      <c r="BO151" s="3"/>
+      <c r="BP151" s="3"/>
+    </row>
+    <row r="152" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C152" s="3"/>
       <c r="D152" s="3"/>
       <c r="E152" s="3"/>
@@ -11225,8 +12008,12 @@
       <c r="BJ152" s="3"/>
       <c r="BK152" s="3"/>
       <c r="BL152" s="3"/>
-    </row>
-    <row r="153" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM152" s="3"/>
+      <c r="BN152" s="3"/>
+      <c r="BO152" s="3"/>
+      <c r="BP152" s="3"/>
+    </row>
+    <row r="153" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C153" s="3"/>
       <c r="D153" s="3"/>
       <c r="E153" s="3"/>
@@ -11289,8 +12076,12 @@
       <c r="BJ153" s="3"/>
       <c r="BK153" s="3"/>
       <c r="BL153" s="3"/>
-    </row>
-    <row r="154" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM153" s="3"/>
+      <c r="BN153" s="3"/>
+      <c r="BO153" s="3"/>
+      <c r="BP153" s="3"/>
+    </row>
+    <row r="154" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C154" s="3"/>
       <c r="D154" s="3"/>
       <c r="E154" s="3"/>
@@ -11353,8 +12144,12 @@
       <c r="BJ154" s="3"/>
       <c r="BK154" s="3"/>
       <c r="BL154" s="3"/>
-    </row>
-    <row r="155" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM154" s="3"/>
+      <c r="BN154" s="3"/>
+      <c r="BO154" s="3"/>
+      <c r="BP154" s="3"/>
+    </row>
+    <row r="155" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C155" s="3"/>
       <c r="D155" s="3"/>
       <c r="E155" s="3"/>
@@ -11417,8 +12212,12 @@
       <c r="BJ155" s="3"/>
       <c r="BK155" s="3"/>
       <c r="BL155" s="3"/>
-    </row>
-    <row r="156" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM155" s="3"/>
+      <c r="BN155" s="3"/>
+      <c r="BO155" s="3"/>
+      <c r="BP155" s="3"/>
+    </row>
+    <row r="156" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C156" s="3"/>
       <c r="D156" s="3"/>
       <c r="E156" s="3"/>
@@ -11481,8 +12280,12 @@
       <c r="BJ156" s="3"/>
       <c r="BK156" s="3"/>
       <c r="BL156" s="3"/>
-    </row>
-    <row r="157" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM156" s="3"/>
+      <c r="BN156" s="3"/>
+      <c r="BO156" s="3"/>
+      <c r="BP156" s="3"/>
+    </row>
+    <row r="157" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C157" s="3"/>
       <c r="D157" s="3"/>
       <c r="E157" s="3"/>
@@ -11545,8 +12348,12 @@
       <c r="BJ157" s="3"/>
       <c r="BK157" s="3"/>
       <c r="BL157" s="3"/>
-    </row>
-    <row r="158" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM157" s="3"/>
+      <c r="BN157" s="3"/>
+      <c r="BO157" s="3"/>
+      <c r="BP157" s="3"/>
+    </row>
+    <row r="158" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C158" s="3"/>
       <c r="D158" s="3"/>
       <c r="E158" s="3"/>
@@ -11609,8 +12416,12 @@
       <c r="BJ158" s="3"/>
       <c r="BK158" s="3"/>
       <c r="BL158" s="3"/>
-    </row>
-    <row r="159" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM158" s="3"/>
+      <c r="BN158" s="3"/>
+      <c r="BO158" s="3"/>
+      <c r="BP158" s="3"/>
+    </row>
+    <row r="159" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C159" s="3"/>
       <c r="D159" s="3"/>
       <c r="E159" s="3"/>
@@ -11673,8 +12484,12 @@
       <c r="BJ159" s="3"/>
       <c r="BK159" s="3"/>
       <c r="BL159" s="3"/>
-    </row>
-    <row r="160" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM159" s="3"/>
+      <c r="BN159" s="3"/>
+      <c r="BO159" s="3"/>
+      <c r="BP159" s="3"/>
+    </row>
+    <row r="160" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C160" s="3"/>
       <c r="D160" s="3"/>
       <c r="E160" s="3"/>
@@ -11737,8 +12552,12 @@
       <c r="BJ160" s="3"/>
       <c r="BK160" s="3"/>
       <c r="BL160" s="3"/>
-    </row>
-    <row r="161" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM160" s="3"/>
+      <c r="BN160" s="3"/>
+      <c r="BO160" s="3"/>
+      <c r="BP160" s="3"/>
+    </row>
+    <row r="161" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C161" s="3"/>
       <c r="D161" s="3"/>
       <c r="E161" s="3"/>
@@ -11801,8 +12620,12 @@
       <c r="BJ161" s="3"/>
       <c r="BK161" s="3"/>
       <c r="BL161" s="3"/>
-    </row>
-    <row r="162" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM161" s="3"/>
+      <c r="BN161" s="3"/>
+      <c r="BO161" s="3"/>
+      <c r="BP161" s="3"/>
+    </row>
+    <row r="162" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C162" s="3"/>
       <c r="D162" s="3"/>
       <c r="E162" s="3"/>
@@ -11865,8 +12688,12 @@
       <c r="BJ162" s="3"/>
       <c r="BK162" s="3"/>
       <c r="BL162" s="3"/>
-    </row>
-    <row r="163" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM162" s="3"/>
+      <c r="BN162" s="3"/>
+      <c r="BO162" s="3"/>
+      <c r="BP162" s="3"/>
+    </row>
+    <row r="163" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C163" s="3"/>
       <c r="D163" s="3"/>
       <c r="E163" s="3"/>
@@ -11929,8 +12756,12 @@
       <c r="BJ163" s="3"/>
       <c r="BK163" s="3"/>
       <c r="BL163" s="3"/>
-    </row>
-    <row r="164" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM163" s="3"/>
+      <c r="BN163" s="3"/>
+      <c r="BO163" s="3"/>
+      <c r="BP163" s="3"/>
+    </row>
+    <row r="164" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C164" s="3"/>
       <c r="D164" s="3"/>
       <c r="E164" s="3"/>
@@ -11993,8 +12824,12 @@
       <c r="BJ164" s="3"/>
       <c r="BK164" s="3"/>
       <c r="BL164" s="3"/>
-    </row>
-    <row r="165" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM164" s="3"/>
+      <c r="BN164" s="3"/>
+      <c r="BO164" s="3"/>
+      <c r="BP164" s="3"/>
+    </row>
+    <row r="165" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C165" s="3"/>
       <c r="D165" s="3"/>
       <c r="E165" s="3"/>
@@ -12057,8 +12892,12 @@
       <c r="BJ165" s="3"/>
       <c r="BK165" s="3"/>
       <c r="BL165" s="3"/>
-    </row>
-    <row r="166" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM165" s="3"/>
+      <c r="BN165" s="3"/>
+      <c r="BO165" s="3"/>
+      <c r="BP165" s="3"/>
+    </row>
+    <row r="166" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C166" s="3"/>
       <c r="D166" s="3"/>
       <c r="E166" s="3"/>
@@ -12121,8 +12960,12 @@
       <c r="BJ166" s="3"/>
       <c r="BK166" s="3"/>
       <c r="BL166" s="3"/>
-    </row>
-    <row r="167" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM166" s="3"/>
+      <c r="BN166" s="3"/>
+      <c r="BO166" s="3"/>
+      <c r="BP166" s="3"/>
+    </row>
+    <row r="167" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C167" s="3"/>
       <c r="D167" s="3"/>
       <c r="E167" s="3"/>
@@ -12185,8 +13028,12 @@
       <c r="BJ167" s="3"/>
       <c r="BK167" s="3"/>
       <c r="BL167" s="3"/>
-    </row>
-    <row r="168" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM167" s="3"/>
+      <c r="BN167" s="3"/>
+      <c r="BO167" s="3"/>
+      <c r="BP167" s="3"/>
+    </row>
+    <row r="168" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C168" s="3"/>
       <c r="D168" s="3"/>
       <c r="E168" s="3"/>
@@ -12249,8 +13096,12 @@
       <c r="BJ168" s="3"/>
       <c r="BK168" s="3"/>
       <c r="BL168" s="3"/>
-    </row>
-    <row r="169" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM168" s="3"/>
+      <c r="BN168" s="3"/>
+      <c r="BO168" s="3"/>
+      <c r="BP168" s="3"/>
+    </row>
+    <row r="169" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C169" s="3"/>
       <c r="D169" s="3"/>
       <c r="E169" s="3"/>
@@ -12313,8 +13164,12 @@
       <c r="BJ169" s="3"/>
       <c r="BK169" s="3"/>
       <c r="BL169" s="3"/>
-    </row>
-    <row r="170" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM169" s="3"/>
+      <c r="BN169" s="3"/>
+      <c r="BO169" s="3"/>
+      <c r="BP169" s="3"/>
+    </row>
+    <row r="170" spans="3:68" x14ac:dyDescent="0.2">
       <c r="C170" s="3"/>
       <c r="D170" s="3"/>
       <c r="E170" s="3"/>
@@ -12377,6 +13232,10 @@
       <c r="BJ170" s="3"/>
       <c r="BK170" s="3"/>
       <c r="BL170" s="3"/>
+      <c r="BM170" s="3"/>
+      <c r="BN170" s="3"/>
+      <c r="BO170" s="3"/>
+      <c r="BP170" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/AMD.xlsx
+++ b/AMD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DC0D06D-4B68-411C-9021-BFB1E001EDAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6682DB51-53BA-4266-9DF3-262A9F8F354D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{88DDBE30-5603-410A-A895-5ECD92172F1B}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="1" xr2:uid="{88DDBE30-5603-410A-A895-5ECD92172F1B}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -217,13 +217,19 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\)"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -312,31 +318,34 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -699,7 +708,7 @@
         <v>1</v>
       </c>
       <c r="K2" s="2">
-        <v>514.87</v>
+        <v>487.7</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
@@ -707,10 +716,10 @@
         <v>2</v>
       </c>
       <c r="K3" s="3">
-        <v>1630.600639</v>
-      </c>
-      <c r="L3" s="18" t="s">
-        <v>53</v>
+        <v>1632.475042</v>
+      </c>
+      <c r="L3" s="19" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
@@ -722,7 +731,7 @@
       </c>
       <c r="K4" s="3">
         <f>+K2*K3</f>
-        <v>839547.35100192996</v>
+        <v>796158.07798339997</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
@@ -730,11 +739,11 @@
         <v>4</v>
       </c>
       <c r="K5" s="3">
-        <f>5575+6762</f>
-        <v>12337</v>
-      </c>
-      <c r="L5" s="18" t="s">
-        <v>53</v>
+        <f>5086+8025</f>
+        <v>13111</v>
+      </c>
+      <c r="L5" s="19" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
@@ -742,11 +751,11 @@
         <v>5</v>
       </c>
       <c r="K6" s="3">
-        <f>874+2350</f>
-        <v>3224</v>
-      </c>
-      <c r="L6" s="18" t="s">
-        <v>53</v>
+        <f>875+2351</f>
+        <v>3226</v>
+      </c>
+      <c r="L6" s="19" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
@@ -755,7 +764,7 @@
       </c>
       <c r="K7" s="3">
         <f>+K4-K5+K6</f>
-        <v>830434.35100192996</v>
+        <v>786273.07798339997</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
@@ -908,7 +917,9 @@
       <c r="O3" s="11">
         <v>5775</v>
       </c>
-      <c r="P3" s="11"/>
+      <c r="P3" s="11">
+        <v>6718</v>
+      </c>
       <c r="Q3" s="11"/>
       <c r="R3" s="11"/>
       <c r="S3" s="11"/>
@@ -1009,7 +1020,9 @@
       <c r="O4" s="11">
         <v>2885</v>
       </c>
-      <c r="P4" s="11"/>
+      <c r="P4" s="11">
+        <v>3062</v>
+      </c>
       <c r="Q4" s="11"/>
       <c r="R4" s="11"/>
       <c r="S4" s="11"/>
@@ -1110,7 +1123,9 @@
       <c r="O5" s="11">
         <v>720</v>
       </c>
-      <c r="P5" s="11"/>
+      <c r="P5" s="11">
+        <v>779</v>
+      </c>
       <c r="Q5" s="11"/>
       <c r="R5" s="11"/>
       <c r="S5" s="11"/>
@@ -1211,7 +1226,9 @@
       <c r="O6" s="11">
         <v>873</v>
       </c>
-      <c r="P6" s="11"/>
+      <c r="P6" s="11">
+        <v>977</v>
+      </c>
       <c r="Q6" s="11"/>
       <c r="R6" s="11"/>
       <c r="S6" s="11"/>
@@ -1313,7 +1330,9 @@
       <c r="O7" s="12">
         <v>10253</v>
       </c>
-      <c r="P7" s="11"/>
+      <c r="P7" s="12">
+        <v>11536</v>
+      </c>
       <c r="Q7" s="11"/>
       <c r="R7" s="11"/>
       <c r="S7" s="11"/>
@@ -1414,7 +1433,9 @@
       <c r="O8" s="11">
         <v>4576</v>
       </c>
-      <c r="P8" s="11"/>
+      <c r="P8" s="11">
+        <v>5073</v>
+      </c>
       <c r="Q8" s="11"/>
       <c r="R8" s="11"/>
       <c r="S8" s="11"/>
@@ -1515,7 +1536,9 @@
       <c r="O9" s="11">
         <v>261</v>
       </c>
-      <c r="P9" s="11"/>
+      <c r="P9" s="11">
+        <v>260</v>
+      </c>
       <c r="Q9" s="11"/>
       <c r="R9" s="11"/>
       <c r="S9" s="11"/>
@@ -1629,7 +1652,10 @@
         <f t="shared" si="3"/>
         <v>5416</v>
       </c>
-      <c r="P10" s="11"/>
+      <c r="P10" s="11">
+        <f t="shared" si="3"/>
+        <v>6203</v>
+      </c>
       <c r="Q10" s="11"/>
       <c r="R10" s="11"/>
       <c r="S10" s="11"/>
@@ -1732,7 +1758,9 @@
       <c r="O11" s="11">
         <v>2397</v>
       </c>
-      <c r="P11" s="11"/>
+      <c r="P11" s="11">
+        <v>2528</v>
+      </c>
       <c r="Q11" s="11"/>
       <c r="R11" s="11"/>
       <c r="S11" s="11"/>
@@ -1833,7 +1861,9 @@
       <c r="O12" s="11">
         <v>1253</v>
       </c>
-      <c r="P12" s="11"/>
+      <c r="P12" s="11">
+        <v>1401</v>
+      </c>
       <c r="Q12" s="11"/>
       <c r="R12" s="11"/>
       <c r="S12" s="11"/>
@@ -1934,7 +1964,9 @@
       <c r="O13" s="11">
         <v>290</v>
       </c>
-      <c r="P13" s="11"/>
+      <c r="P13" s="11">
+        <v>284</v>
+      </c>
       <c r="Q13" s="11"/>
       <c r="R13" s="11"/>
       <c r="S13" s="11"/>
@@ -2035,7 +2067,9 @@
       <c r="O14" s="11">
         <v>0</v>
       </c>
-      <c r="P14" s="11"/>
+      <c r="P14" s="11">
+        <v>0</v>
+      </c>
       <c r="Q14" s="11"/>
       <c r="R14" s="11"/>
       <c r="S14" s="11"/>
@@ -2149,7 +2183,10 @@
         <f t="shared" si="5"/>
         <v>1476</v>
       </c>
-      <c r="P15" s="11"/>
+      <c r="P15" s="11">
+        <f t="shared" si="5"/>
+        <v>1990</v>
+      </c>
       <c r="Q15" s="11"/>
       <c r="R15" s="11"/>
       <c r="S15" s="11"/>
@@ -2252,7 +2289,9 @@
       <c r="O16" s="11">
         <v>37</v>
       </c>
-      <c r="P16" s="11"/>
+      <c r="P16" s="11">
+        <v>37</v>
+      </c>
       <c r="Q16" s="11"/>
       <c r="R16" s="11"/>
       <c r="S16" s="11"/>
@@ -2353,7 +2392,9 @@
       <c r="O17" s="11">
         <v>165</v>
       </c>
-      <c r="P17" s="11"/>
+      <c r="P17" s="11">
+        <v>598</v>
+      </c>
       <c r="Q17" s="11"/>
       <c r="R17" s="11"/>
       <c r="S17" s="11"/>
@@ -2467,7 +2508,10 @@
         <f t="shared" si="7"/>
         <v>1604</v>
       </c>
-      <c r="P18" s="11"/>
+      <c r="P18" s="11">
+        <f t="shared" si="7"/>
+        <v>2551</v>
+      </c>
       <c r="Q18" s="11"/>
       <c r="R18" s="11"/>
       <c r="S18" s="11"/>
@@ -2570,7 +2614,9 @@
       <c r="O19" s="11">
         <v>238</v>
       </c>
-      <c r="P19" s="11"/>
+      <c r="P19" s="11">
+        <v>252</v>
+      </c>
       <c r="Q19" s="11"/>
       <c r="R19" s="11"/>
       <c r="S19" s="11"/>
@@ -2674,7 +2720,10 @@
         <f>6+11</f>
         <v>17</v>
       </c>
-      <c r="P20" s="11"/>
+      <c r="P20" s="11">
+        <f>6-8</f>
+        <v>-2</v>
+      </c>
       <c r="Q20" s="11"/>
       <c r="R20" s="11"/>
       <c r="S20" s="11"/>
@@ -2789,7 +2838,10 @@
         <f t="shared" si="9"/>
         <v>1383</v>
       </c>
-      <c r="P21" s="11"/>
+      <c r="P21" s="11">
+        <f t="shared" si="9"/>
+        <v>2297</v>
+      </c>
       <c r="Q21" s="11"/>
       <c r="R21" s="11"/>
       <c r="S21" s="11"/>
@@ -2973,7 +3025,10 @@
         <f t="shared" si="11"/>
         <v>0.8479460453709381</v>
       </c>
-      <c r="P23" s="7"/>
+      <c r="P23" s="7">
+        <f t="shared" si="11"/>
+        <v>1.4074754901960784</v>
+      </c>
       <c r="Q23" s="7"/>
       <c r="R23" s="7"/>
       <c r="S23" s="3"/>
@@ -3074,7 +3129,9 @@
       <c r="O24" s="3">
         <v>1631</v>
       </c>
-      <c r="P24" s="3"/>
+      <c r="P24" s="3">
+        <v>1632</v>
+      </c>
       <c r="Q24" s="3"/>
       <c r="R24" s="3"/>
       <c r="S24" s="3"/>
@@ -3221,7 +3278,7 @@
         <v>0.17568965517241386</v>
       </c>
       <c r="J26" s="13" t="e">
-        <f t="shared" ref="J26:O26" si="13">+J7/F7-1</f>
+        <f t="shared" ref="J26:P26" si="13">+J7/F7-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K26" s="13">
@@ -3244,7 +3301,10 @@
         <f t="shared" si="13"/>
         <v>0.37846195213767131</v>
       </c>
-      <c r="P26" s="13"/>
+      <c r="P26" s="13">
+        <f t="shared" si="13"/>
+        <v>0.5011060507482108</v>
+      </c>
       <c r="Q26" s="13"/>
       <c r="R26" s="13"/>
       <c r="S26" s="3"/>
@@ -3354,10 +3414,13 @@
         <v>0.54303797468354431</v>
       </c>
       <c r="O27" s="8">
-        <f t="shared" ref="O27" si="16">+O10/O7</f>
+        <f t="shared" ref="O27:P27" si="16">+O10/O7</f>
         <v>0.52823563834975129</v>
       </c>
-      <c r="P27" s="8"/>
+      <c r="P27" s="8">
+        <f t="shared" si="16"/>
+        <v>0.53770804438280162</v>
+      </c>
       <c r="Q27" s="8"/>
       <c r="R27" s="8"/>
       <c r="S27" s="3"/>
@@ -3470,10 +3533,13 @@
         <v>0.17059396299902629</v>
       </c>
       <c r="O28" s="8">
-        <f t="shared" ref="O28" si="20">+O15/O7</f>
+        <f t="shared" ref="O28:P28" si="20">+O15/O7</f>
         <v>0.14395786599044183</v>
       </c>
-      <c r="P28" s="8"/>
+      <c r="P28" s="8">
+        <f t="shared" si="20"/>
+        <v>0.17250346740638003</v>
+      </c>
       <c r="Q28" s="8"/>
       <c r="R28" s="8"/>
       <c r="S28" s="3"/>
@@ -3586,10 +3652,13 @@
         <v>0.21938283510125361</v>
       </c>
       <c r="O29" s="8">
-        <f t="shared" ref="O29" si="24">+O19/O18</f>
+        <f t="shared" ref="O29:P29" si="24">+O19/O18</f>
         <v>0.14837905236907731</v>
       </c>
-      <c r="P29" s="8"/>
+      <c r="P29" s="8">
+        <f t="shared" si="24"/>
+        <v>9.8784790278322224E-2</v>
+      </c>
       <c r="Q29" s="8"/>
       <c r="R29" s="8"/>
       <c r="S29" s="3"/>
